--- a/Odeme.xlsx
+++ b/Odeme.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://clbexch-my.sharepoint.com/personal/serdar_gunizi_celebiaviation_com/Documents/Personel/Programming/Python/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{028C6BA9-E504-4CA6-9D1E-EA28749E249E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="8_{028C6BA9-E504-4CA6-9D1E-EA28749E249E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{316875F9-CC7C-49DE-B846-FF5FC587BAC4}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{8342C7F8-B62A-427E-B7BD-BDD92660C0AC}"/>
   </bookViews>
@@ -1223,10 +1223,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1561,14 +1562,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DDBFB41B-2FC1-43D5-8050-DA58EFE3045A}">
-  <dimension ref="A1:E1034"/>
+  <dimension ref="A1:E696"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="22.7265625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.08984375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="34.6328125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.453125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.453125" style="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.35">
@@ -1584,7 +1585,7 @@
       <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>1</v>
       </c>
     </row>
@@ -1601,7 +1602,7 @@
       <c r="D2" t="s">
         <v>8</v>
       </c>
-      <c r="E2">
+      <c r="E2" s="3">
         <v>-224094.71</v>
       </c>
     </row>
@@ -1618,7 +1619,7 @@
       <c r="D3" t="s">
         <v>10</v>
       </c>
-      <c r="E3">
+      <c r="E3" s="3">
         <v>2150</v>
       </c>
     </row>
@@ -1635,7 +1636,7 @@
       <c r="D4" t="s">
         <v>11</v>
       </c>
-      <c r="E4">
+      <c r="E4" s="3">
         <v>242</v>
       </c>
     </row>
@@ -1652,7 +1653,7 @@
       <c r="D5" t="s">
         <v>13</v>
       </c>
-      <c r="E5">
+      <c r="E5" s="3">
         <v>100846.48</v>
       </c>
     </row>
@@ -1669,7 +1670,7 @@
       <c r="D6" t="s">
         <v>15</v>
       </c>
-      <c r="E6">
+      <c r="E6" s="3">
         <v>515</v>
       </c>
     </row>
@@ -1686,7 +1687,7 @@
       <c r="D7" t="s">
         <v>17</v>
       </c>
-      <c r="E7">
+      <c r="E7" s="3">
         <v>1925.89</v>
       </c>
     </row>
@@ -1703,7 +1704,7 @@
       <c r="D8" t="s">
         <v>19</v>
       </c>
-      <c r="E8">
+      <c r="E8" s="3">
         <v>31666.3</v>
       </c>
     </row>
@@ -1720,7 +1721,7 @@
       <c r="D9" t="s">
         <v>11</v>
       </c>
-      <c r="E9">
+      <c r="E9" s="3">
         <v>331.5</v>
       </c>
     </row>
@@ -1737,7 +1738,7 @@
       <c r="D10" t="s">
         <v>21</v>
       </c>
-      <c r="E10">
+      <c r="E10" s="3">
         <v>2700</v>
       </c>
     </row>
@@ -1754,7 +1755,7 @@
       <c r="D11" t="s">
         <v>8</v>
       </c>
-      <c r="E11">
+      <c r="E11" s="3">
         <v>-344613.89</v>
       </c>
     </row>
@@ -1771,7 +1772,7 @@
       <c r="D12" t="s">
         <v>24</v>
       </c>
-      <c r="E12">
+      <c r="E12" s="3">
         <v>3990</v>
       </c>
     </row>
@@ -1788,7 +1789,7 @@
       <c r="D13" t="s">
         <v>15</v>
       </c>
-      <c r="E13">
+      <c r="E13" s="3">
         <v>612.75</v>
       </c>
     </row>
@@ -1805,7 +1806,7 @@
       <c r="D14" t="s">
         <v>27</v>
       </c>
-      <c r="E14">
+      <c r="E14" s="3">
         <v>567</v>
       </c>
     </row>
@@ -1822,7 +1823,7 @@
       <c r="D15" t="s">
         <v>13</v>
       </c>
-      <c r="E15">
+      <c r="E15" s="3">
         <v>34581.699999999997</v>
       </c>
     </row>
@@ -1839,7 +1840,7 @@
       <c r="D16" t="s">
         <v>13</v>
       </c>
-      <c r="E16">
+      <c r="E16" s="3">
         <v>129148.79</v>
       </c>
     </row>
@@ -1856,7 +1857,7 @@
       <c r="D17" t="s">
         <v>15</v>
       </c>
-      <c r="E17">
+      <c r="E17" s="3">
         <v>254.5</v>
       </c>
     </row>
@@ -1873,7 +1874,7 @@
       <c r="D18" t="s">
         <v>32</v>
       </c>
-      <c r="E18">
+      <c r="E18" s="3">
         <v>5528.6</v>
       </c>
     </row>
@@ -1890,7 +1891,7 @@
       <c r="D19" t="s">
         <v>33</v>
       </c>
-      <c r="E19">
+      <c r="E19" s="3">
         <v>378.54</v>
       </c>
     </row>
@@ -1907,7 +1908,7 @@
       <c r="D20" t="s">
         <v>35</v>
       </c>
-      <c r="E20">
+      <c r="E20" s="3">
         <v>2830</v>
       </c>
     </row>
@@ -1924,7 +1925,7 @@
       <c r="D21" t="s">
         <v>36</v>
       </c>
-      <c r="E21">
+      <c r="E21" s="3">
         <v>31666.3</v>
       </c>
     </row>
@@ -1941,7 +1942,7 @@
       <c r="D22" t="s">
         <v>10</v>
       </c>
-      <c r="E22">
+      <c r="E22" s="3">
         <v>2160</v>
       </c>
     </row>
@@ -1958,7 +1959,7 @@
       <c r="D23" t="s">
         <v>37</v>
       </c>
-      <c r="E23">
+      <c r="E23" s="3">
         <v>9676.5300000000007</v>
       </c>
     </row>
@@ -1975,7 +1976,7 @@
       <c r="D24" t="s">
         <v>8</v>
       </c>
-      <c r="E24">
+      <c r="E24" s="3">
         <v>-145280.78</v>
       </c>
     </row>
@@ -1992,7 +1993,7 @@
       <c r="D25" t="s">
         <v>13</v>
       </c>
-      <c r="E25">
+      <c r="E25" s="3">
         <v>373301.01</v>
       </c>
     </row>
@@ -2009,7 +2010,7 @@
       <c r="D26" t="s">
         <v>8</v>
       </c>
-      <c r="E26">
+      <c r="E26" s="3">
         <v>-80000</v>
       </c>
     </row>
@@ -2026,7 +2027,7 @@
       <c r="D27" t="s">
         <v>8</v>
       </c>
-      <c r="E27">
+      <c r="E27" s="3">
         <v>-50000</v>
       </c>
     </row>
@@ -2043,7 +2044,7 @@
       <c r="D28" t="s">
         <v>42</v>
       </c>
-      <c r="E28">
+      <c r="E28" s="3">
         <v>359</v>
       </c>
     </row>
@@ -2060,7 +2061,7 @@
       <c r="D29" t="s">
         <v>8</v>
       </c>
-      <c r="E29">
+      <c r="E29" s="3">
         <v>-50000</v>
       </c>
     </row>
@@ -2077,7 +2078,7 @@
       <c r="D30" t="s">
         <v>42</v>
       </c>
-      <c r="E30">
+      <c r="E30" s="3">
         <v>605.5</v>
       </c>
     </row>
@@ -2094,7 +2095,7 @@
       <c r="D31" t="s">
         <v>13</v>
       </c>
-      <c r="E31">
+      <c r="E31" s="3">
         <v>115598.38</v>
       </c>
     </row>
@@ -2111,7 +2112,7 @@
       <c r="D32" t="s">
         <v>15</v>
       </c>
-      <c r="E32">
+      <c r="E32" s="3">
         <v>348.5</v>
       </c>
     </row>
@@ -2128,7 +2129,7 @@
       <c r="D33" t="s">
         <v>48</v>
       </c>
-      <c r="E33">
+      <c r="E33" s="3">
         <v>31666.400000000001</v>
       </c>
     </row>
@@ -2145,7 +2146,7 @@
       <c r="D34" t="s">
         <v>35</v>
       </c>
-      <c r="E34">
+      <c r="E34" s="3">
         <v>2735.1</v>
       </c>
     </row>
@@ -2162,7 +2163,7 @@
       <c r="D35" t="s">
         <v>53</v>
       </c>
-      <c r="E35">
+      <c r="E35" s="3">
         <v>45197.440000000002</v>
       </c>
     </row>
@@ -2179,7 +2180,7 @@
       <c r="D36" t="s">
         <v>54</v>
       </c>
-      <c r="E36">
+      <c r="E36" s="3">
         <v>-59806.720000000001</v>
       </c>
     </row>
@@ -2196,7 +2197,7 @@
       <c r="D37" t="s">
         <v>55</v>
       </c>
-      <c r="E37">
+      <c r="E37" s="3">
         <v>-20960.099999999999</v>
       </c>
     </row>
@@ -2213,7 +2214,7 @@
       <c r="D38" t="s">
         <v>56</v>
       </c>
-      <c r="E38">
+      <c r="E38" s="3">
         <v>-30990.98</v>
       </c>
     </row>
@@ -2230,7 +2231,7 @@
       <c r="D39" t="s">
         <v>57</v>
       </c>
-      <c r="E39">
+      <c r="E39" s="3">
         <v>34830</v>
       </c>
     </row>
@@ -2247,7 +2248,7 @@
       <c r="D40" t="s">
         <v>58</v>
       </c>
-      <c r="E40">
+      <c r="E40" s="3">
         <v>17700</v>
       </c>
     </row>
@@ -2264,7 +2265,7 @@
       <c r="D41" t="s">
         <v>59</v>
       </c>
-      <c r="E41">
+      <c r="E41" s="3">
         <v>-3000</v>
       </c>
     </row>
@@ -2281,7 +2282,7 @@
       <c r="D42" t="s">
         <v>57</v>
       </c>
-      <c r="E42">
+      <c r="E42" s="3">
         <v>300153.28999999998</v>
       </c>
     </row>
@@ -2298,7 +2299,7 @@
       <c r="D43" t="s">
         <v>60</v>
       </c>
-      <c r="E43">
+      <c r="E43" s="3">
         <v>-54270.96</v>
       </c>
     </row>
@@ -2315,7 +2316,7 @@
       <c r="D44" t="s">
         <v>61</v>
       </c>
-      <c r="E44">
+      <c r="E44" s="3">
         <v>-22494.94</v>
       </c>
     </row>
@@ -2332,7 +2333,7 @@
       <c r="D45" t="s">
         <v>62</v>
       </c>
-      <c r="E45">
+      <c r="E45" s="3">
         <v>-35887.410000000003</v>
       </c>
     </row>
@@ -2349,7 +2350,7 @@
       <c r="D46" t="s">
         <v>63</v>
       </c>
-      <c r="E46">
+      <c r="E46" s="3">
         <v>-14494.01</v>
       </c>
     </row>
@@ -2366,7 +2367,7 @@
       <c r="D47" t="s">
         <v>64</v>
       </c>
-      <c r="E47">
+      <c r="E47" s="3">
         <v>-26090.33</v>
       </c>
     </row>
@@ -2383,7 +2384,7 @@
       <c r="D48" t="s">
         <v>65</v>
       </c>
-      <c r="E48">
+      <c r="E48" s="3">
         <v>-11760.05</v>
       </c>
     </row>
@@ -2400,7 +2401,7 @@
       <c r="D49" t="s">
         <v>66</v>
       </c>
-      <c r="E49">
+      <c r="E49" s="3">
         <v>-6720.04</v>
       </c>
     </row>
@@ -2417,7 +2418,7 @@
       <c r="D50" t="s">
         <v>67</v>
       </c>
-      <c r="E50">
+      <c r="E50" s="3">
         <v>-5874.67</v>
       </c>
     </row>
@@ -2434,7 +2435,7 @@
       <c r="D51" t="s">
         <v>68</v>
       </c>
-      <c r="E51">
+      <c r="E51" s="3">
         <v>-80000</v>
       </c>
     </row>
@@ -2451,7 +2452,7 @@
       <c r="D52" t="s">
         <v>69</v>
       </c>
-      <c r="E52">
+      <c r="E52" s="3">
         <v>9300</v>
       </c>
     </row>
@@ -2468,7 +2469,7 @@
       <c r="D53" t="s">
         <v>70</v>
       </c>
-      <c r="E53">
+      <c r="E53" s="3">
         <v>-509</v>
       </c>
     </row>
@@ -2485,7 +2486,7 @@
       <c r="D54" t="s">
         <v>57</v>
       </c>
-      <c r="E54">
+      <c r="E54" s="3">
         <v>104244.08</v>
       </c>
     </row>
@@ -2502,7 +2503,7 @@
       <c r="D55" t="s">
         <v>68</v>
       </c>
-      <c r="E55">
+      <c r="E55" s="3">
         <v>-50000</v>
       </c>
     </row>
@@ -2519,7 +2520,7 @@
       <c r="D56" t="s">
         <v>71</v>
       </c>
-      <c r="E56">
+      <c r="E56" s="3">
         <v>5650</v>
       </c>
     </row>
@@ -2536,7 +2537,7 @@
       <c r="D57" t="s">
         <v>73</v>
       </c>
-      <c r="E57">
+      <c r="E57" s="3">
         <v>6850</v>
       </c>
     </row>
@@ -2553,7 +2554,7 @@
       <c r="D58" t="s">
         <v>75</v>
       </c>
-      <c r="E58">
+      <c r="E58" s="3">
         <v>14300</v>
       </c>
     </row>
@@ -2570,7 +2571,7 @@
       <c r="D59" t="s">
         <v>57</v>
       </c>
-      <c r="E59">
+      <c r="E59" s="3">
         <v>183135.98</v>
       </c>
     </row>
@@ -2587,7 +2588,7 @@
       <c r="D60" t="s">
         <v>77</v>
       </c>
-      <c r="E60">
+      <c r="E60" s="3">
         <v>-58826.02</v>
       </c>
     </row>
@@ -2604,7 +2605,7 @@
       <c r="D61" t="s">
         <v>78</v>
       </c>
-      <c r="E61">
+      <c r="E61" s="3">
         <v>-23023.39</v>
       </c>
     </row>
@@ -2621,7 +2622,7 @@
       <c r="D62" t="s">
         <v>79</v>
       </c>
-      <c r="E62">
+      <c r="E62" s="3">
         <v>-39815.85</v>
       </c>
     </row>
@@ -2638,7 +2639,7 @@
       <c r="D63" t="s">
         <v>80</v>
       </c>
-      <c r="E63">
+      <c r="E63" s="3">
         <v>-16684.73</v>
       </c>
     </row>
@@ -2655,7 +2656,7 @@
       <c r="D64" t="s">
         <v>81</v>
       </c>
-      <c r="E64">
+      <c r="E64" s="3">
         <v>-14515.06</v>
       </c>
     </row>
@@ -2672,7 +2673,7 @@
       <c r="D65" t="s">
         <v>82</v>
       </c>
-      <c r="E65">
+      <c r="E65" s="3">
         <v>-10352</v>
       </c>
     </row>
@@ -2689,7 +2690,7 @@
       <c r="D66" t="s">
         <v>83</v>
       </c>
-      <c r="E66">
+      <c r="E66" s="3">
         <v>-972.13</v>
       </c>
     </row>
@@ -2706,7 +2707,7 @@
       <c r="D67" t="s">
         <v>84</v>
       </c>
-      <c r="E67">
+      <c r="E67" s="3">
         <v>-13922.05</v>
       </c>
     </row>
@@ -2723,7 +2724,7 @@
       <c r="D68" t="s">
         <v>85</v>
       </c>
-      <c r="E68">
+      <c r="E68" s="3">
         <v>-4331.3900000000003</v>
       </c>
     </row>
@@ -2740,7 +2741,7 @@
       <c r="D69" t="s">
         <v>86</v>
       </c>
-      <c r="E69">
+      <c r="E69" s="3">
         <v>-73000</v>
       </c>
     </row>
@@ -2757,7 +2758,7 @@
       <c r="D70" t="s">
         <v>87</v>
       </c>
-      <c r="E70">
+      <c r="E70" s="3">
         <v>3900</v>
       </c>
     </row>
@@ -2774,7 +2775,7 @@
       <c r="D71" t="s">
         <v>57</v>
       </c>
-      <c r="E71">
+      <c r="E71" s="3">
         <v>26805</v>
       </c>
     </row>
@@ -2791,7 +2792,7 @@
       <c r="D72" t="s">
         <v>89</v>
       </c>
-      <c r="E72">
+      <c r="E72" s="3">
         <v>-179</v>
       </c>
     </row>
@@ -2808,7 +2809,7 @@
       <c r="D73" t="s">
         <v>90</v>
       </c>
-      <c r="E73">
+      <c r="E73" s="3">
         <v>-179</v>
       </c>
     </row>
@@ -2825,7 +2826,7 @@
       <c r="D74" t="s">
         <v>57</v>
       </c>
-      <c r="E74">
+      <c r="E74" s="3">
         <v>46710</v>
       </c>
     </row>
@@ -2842,7 +2843,7 @@
       <c r="D75" t="s">
         <v>68</v>
       </c>
-      <c r="E75">
+      <c r="E75" s="3">
         <v>-50000</v>
       </c>
     </row>
@@ -2859,7 +2860,7 @@
       <c r="D76" t="s">
         <v>57</v>
       </c>
-      <c r="E76">
+      <c r="E76" s="3">
         <v>40008.019999999997</v>
       </c>
     </row>
@@ -2876,7 +2877,7 @@
       <c r="D77" t="s">
         <v>91</v>
       </c>
-      <c r="E77">
+      <c r="E77" s="3">
         <v>15800</v>
       </c>
     </row>
@@ -2893,7 +2894,7 @@
       <c r="D78" t="s">
         <v>93</v>
       </c>
-      <c r="E78">
+      <c r="E78" s="3">
         <v>15700</v>
       </c>
     </row>
@@ -2910,7 +2911,7 @@
       <c r="D79" t="s">
         <v>57</v>
       </c>
-      <c r="E79">
+      <c r="E79" s="3">
         <v>131617.79</v>
       </c>
     </row>
@@ -2927,7 +2928,7 @@
       <c r="D80" t="s">
         <v>94</v>
       </c>
-      <c r="E80">
+      <c r="E80" s="3">
         <v>-182683.45</v>
       </c>
     </row>
@@ -2944,7 +2945,7 @@
       <c r="D81" t="s">
         <v>95</v>
       </c>
-      <c r="E81">
+      <c r="E81" s="3">
         <v>5700</v>
       </c>
     </row>
@@ -2961,7 +2962,7 @@
       <c r="D82" t="s">
         <v>57</v>
       </c>
-      <c r="E82">
+      <c r="E82" s="3">
         <v>61900</v>
       </c>
     </row>
@@ -2978,7 +2979,7 @@
       <c r="D83" t="s">
         <v>97</v>
       </c>
-      <c r="E83">
+      <c r="E83" s="3">
         <v>15400</v>
       </c>
     </row>
@@ -2995,7 +2996,7 @@
       <c r="D84" t="s">
         <v>57</v>
       </c>
-      <c r="E84">
+      <c r="E84" s="3">
         <v>48551</v>
       </c>
     </row>
@@ -3012,7 +3013,7 @@
       <c r="D85" t="s">
         <v>99</v>
       </c>
-      <c r="E85">
+      <c r="E85" s="3">
         <v>-76905.460000000006</v>
       </c>
     </row>
@@ -3029,7 +3030,7 @@
       <c r="D86" t="s">
         <v>100</v>
       </c>
-      <c r="E86">
+      <c r="E86" s="3">
         <v>-32886.269999999997</v>
       </c>
     </row>
@@ -3046,7 +3047,7 @@
       <c r="D87" t="s">
         <v>101</v>
       </c>
-      <c r="E87">
+      <c r="E87" s="3">
         <v>-18416.349999999999</v>
       </c>
     </row>
@@ -3063,7 +3064,7 @@
       <c r="D88" t="s">
         <v>102</v>
       </c>
-      <c r="E88">
+      <c r="E88" s="3">
         <v>-26473.31</v>
       </c>
     </row>
@@ -3080,7 +3081,7 @@
       <c r="D89" t="s">
         <v>103</v>
       </c>
-      <c r="E89">
+      <c r="E89" s="3">
         <v>-6706.9</v>
       </c>
     </row>
@@ -3097,7 +3098,7 @@
       <c r="D90" t="s">
         <v>57</v>
       </c>
-      <c r="E90">
+      <c r="E90" s="3">
         <v>39041</v>
       </c>
     </row>
@@ -3114,7 +3115,7 @@
       <c r="D91" t="s">
         <v>105</v>
       </c>
-      <c r="E91">
+      <c r="E91" s="3">
         <v>5600</v>
       </c>
     </row>
@@ -3131,7 +3132,7 @@
       <c r="D92" t="s">
         <v>57</v>
       </c>
-      <c r="E92">
+      <c r="E92" s="3">
         <v>88207.81</v>
       </c>
     </row>
@@ -3148,7 +3149,7 @@
       <c r="D93" t="s">
         <v>106</v>
       </c>
-      <c r="E93">
+      <c r="E93" s="3">
         <v>-15000</v>
       </c>
     </row>
@@ -3165,7 +3166,7 @@
       <c r="D94" t="s">
         <v>57</v>
       </c>
-      <c r="E94">
+      <c r="E94" s="3">
         <v>159090.95000000001</v>
       </c>
     </row>
@@ -3182,7 +3183,7 @@
       <c r="D95" t="s">
         <v>107</v>
       </c>
-      <c r="E95">
+      <c r="E95" s="3">
         <v>-6770.56</v>
       </c>
     </row>
@@ -3199,7 +3200,7 @@
       <c r="D96" t="s">
         <v>108</v>
       </c>
-      <c r="E96">
+      <c r="E96" s="3">
         <v>-58288.74</v>
       </c>
     </row>
@@ -3216,7 +3217,7 @@
       <c r="D97" t="s">
         <v>109</v>
       </c>
-      <c r="E97">
+      <c r="E97" s="3">
         <v>-27262.38</v>
       </c>
     </row>
@@ -3233,7 +3234,7 @@
       <c r="D98" t="s">
         <v>110</v>
       </c>
-      <c r="E98">
+      <c r="E98" s="3">
         <v>-23925.22</v>
       </c>
     </row>
@@ -3250,7 +3251,7 @@
       <c r="D99" t="s">
         <v>111</v>
       </c>
-      <c r="E99">
+      <c r="E99" s="3">
         <v>-17246.599999999999</v>
       </c>
     </row>
@@ -3267,7 +3268,7 @@
       <c r="D100" t="s">
         <v>112</v>
       </c>
-      <c r="E100">
+      <c r="E100" s="3">
         <v>-7997.97</v>
       </c>
     </row>
@@ -3284,7 +3285,7 @@
       <c r="D101" t="s">
         <v>113</v>
       </c>
-      <c r="E101">
+      <c r="E101" s="3">
         <v>-3029.5</v>
       </c>
     </row>
@@ -3301,7 +3302,7 @@
       <c r="D102" t="s">
         <v>114</v>
       </c>
-      <c r="E102">
+      <c r="E102" s="3">
         <v>-10473.15</v>
       </c>
     </row>
@@ -3318,7 +3319,7 @@
       <c r="D103" t="s">
         <v>115</v>
       </c>
-      <c r="E103">
+      <c r="E103" s="3">
         <v>-4009.7</v>
       </c>
     </row>
@@ -3335,7 +3336,7 @@
       <c r="D104" t="s">
         <v>116</v>
       </c>
-      <c r="E104">
+      <c r="E104" s="3">
         <v>4900</v>
       </c>
     </row>
@@ -3352,7 +3353,7 @@
       <c r="D105" t="s">
         <v>57</v>
       </c>
-      <c r="E105">
+      <c r="E105" s="3">
         <v>45830</v>
       </c>
     </row>
@@ -3369,7 +3370,7 @@
       <c r="D106" t="s">
         <v>118</v>
       </c>
-      <c r="E106">
+      <c r="E106" s="3">
         <v>14550</v>
       </c>
     </row>
@@ -3386,7 +3387,7 @@
       <c r="D107" t="s">
         <v>57</v>
       </c>
-      <c r="E107">
+      <c r="E107" s="3">
         <v>33775</v>
       </c>
     </row>
@@ -3403,7 +3404,7 @@
       <c r="D108" t="s">
         <v>120</v>
       </c>
-      <c r="E108">
+      <c r="E108" s="3">
         <v>-128560.32000000001</v>
       </c>
     </row>
@@ -3420,7 +3421,7 @@
       <c r="D109" t="s">
         <v>121</v>
       </c>
-      <c r="E109">
+      <c r="E109" s="3">
         <v>-8133</v>
       </c>
     </row>
@@ -3437,7 +3438,7 @@
       <c r="D110" t="s">
         <v>57</v>
       </c>
-      <c r="E110">
+      <c r="E110" s="3">
         <v>43392.5</v>
       </c>
     </row>
@@ -3454,7 +3455,7 @@
       <c r="D111" t="s">
         <v>57</v>
       </c>
-      <c r="E111">
+      <c r="E111" s="3">
         <v>42685</v>
       </c>
     </row>
@@ -3471,7 +3472,7 @@
       <c r="D112" t="s">
         <v>122</v>
       </c>
-      <c r="E112">
+      <c r="E112" s="3">
         <v>110000</v>
       </c>
     </row>
@@ -3488,7 +3489,7 @@
       <c r="D113" t="s">
         <v>123</v>
       </c>
-      <c r="E113">
+      <c r="E113" s="3">
         <v>-65120.43</v>
       </c>
     </row>
@@ -3505,7 +3506,7 @@
       <c r="D114" t="s">
         <v>124</v>
       </c>
-      <c r="E114">
+      <c r="E114" s="3">
         <v>-47093.89</v>
       </c>
     </row>
@@ -3522,7 +3523,7 @@
       <c r="D115" t="s">
         <v>57</v>
       </c>
-      <c r="E115">
+      <c r="E115" s="3">
         <v>44195</v>
       </c>
     </row>
@@ -3539,7 +3540,7 @@
       <c r="D116" t="s">
         <v>126</v>
       </c>
-      <c r="E116">
+      <c r="E116" s="3">
         <v>-10200</v>
       </c>
     </row>
@@ -3556,7 +3557,7 @@
       <c r="D117" t="s">
         <v>127</v>
       </c>
-      <c r="E117">
+      <c r="E117" s="3">
         <v>-255426.95</v>
       </c>
     </row>
@@ -3573,7 +3574,7 @@
       <c r="D118" t="s">
         <v>128</v>
       </c>
-      <c r="E118">
+      <c r="E118" s="3">
         <v>22900</v>
       </c>
     </row>
@@ -3590,7 +3591,7 @@
       <c r="D119" t="s">
         <v>57</v>
       </c>
-      <c r="E119">
+      <c r="E119" s="3">
         <v>40860</v>
       </c>
     </row>
@@ -3607,7 +3608,7 @@
       <c r="D120" t="s">
         <v>130</v>
       </c>
-      <c r="E120">
+      <c r="E120" s="3">
         <v>-41211.67</v>
       </c>
     </row>
@@ -3624,7 +3625,7 @@
       <c r="D121" t="s">
         <v>131</v>
       </c>
-      <c r="E121">
+      <c r="E121" s="3">
         <v>-18684.16</v>
       </c>
     </row>
@@ -3641,7 +3642,7 @@
       <c r="D122" t="s">
         <v>132</v>
       </c>
-      <c r="E122">
+      <c r="E122" s="3">
         <v>-11910.43</v>
       </c>
     </row>
@@ -3658,7 +3659,7 @@
       <c r="D123" t="s">
         <v>133</v>
       </c>
-      <c r="E123">
+      <c r="E123" s="3">
         <v>-5918.1</v>
       </c>
     </row>
@@ -3675,7 +3676,7 @@
       <c r="D124" t="s">
         <v>134</v>
       </c>
-      <c r="E124">
+      <c r="E124" s="3">
         <v>5900</v>
       </c>
     </row>
@@ -3692,7 +3693,7 @@
       <c r="D125" t="s">
         <v>57</v>
       </c>
-      <c r="E125">
+      <c r="E125" s="3">
         <v>51950</v>
       </c>
     </row>
@@ -3709,7 +3710,7 @@
       <c r="D126" t="s">
         <v>136</v>
       </c>
-      <c r="E126">
+      <c r="E126" s="3">
         <v>7800</v>
       </c>
     </row>
@@ -3726,7 +3727,7 @@
       <c r="D127" t="s">
         <v>138</v>
       </c>
-      <c r="E127">
+      <c r="E127" s="3">
         <v>33900</v>
       </c>
     </row>
@@ -3743,7 +3744,7 @@
       <c r="D128" t="s">
         <v>139</v>
       </c>
-      <c r="E128">
+      <c r="E128" s="3">
         <v>400</v>
       </c>
     </row>
@@ -3760,7 +3761,7 @@
       <c r="D129" t="s">
         <v>57</v>
       </c>
-      <c r="E129">
+      <c r="E129" s="3">
         <v>190846.59</v>
       </c>
     </row>
@@ -3777,7 +3778,7 @@
       <c r="D130" t="s">
         <v>68</v>
       </c>
-      <c r="E130">
+      <c r="E130" s="3">
         <v>-344613.89</v>
       </c>
     </row>
@@ -3794,7 +3795,7 @@
       <c r="D131" t="s">
         <v>141</v>
       </c>
-      <c r="E131">
+      <c r="E131" s="3">
         <v>12400</v>
       </c>
     </row>
@@ -3811,7 +3812,7 @@
       <c r="D132" t="s">
         <v>57</v>
       </c>
-      <c r="E132">
+      <c r="E132" s="3">
         <v>31332.5</v>
       </c>
     </row>
@@ -3828,7 +3829,7 @@
       <c r="D133" t="s">
         <v>143</v>
       </c>
-      <c r="E133">
+      <c r="E133" s="3">
         <v>9600</v>
       </c>
     </row>
@@ -3845,7 +3846,7 @@
       <c r="D134" t="s">
         <v>57</v>
       </c>
-      <c r="E134">
+      <c r="E134" s="3">
         <v>141632.18</v>
       </c>
     </row>
@@ -3862,7 +3863,7 @@
       <c r="D135" t="s">
         <v>145</v>
       </c>
-      <c r="E135">
+      <c r="E135" s="3">
         <v>-60868.62</v>
       </c>
     </row>
@@ -3879,7 +3880,7 @@
       <c r="D136" t="s">
         <v>146</v>
       </c>
-      <c r="E136">
+      <c r="E136" s="3">
         <v>-41981.46</v>
       </c>
     </row>
@@ -3896,7 +3897,7 @@
       <c r="D137" t="s">
         <v>147</v>
       </c>
-      <c r="E137">
+      <c r="E137" s="3">
         <v>-31917.95</v>
       </c>
     </row>
@@ -3913,7 +3914,7 @@
       <c r="D138" t="s">
         <v>148</v>
       </c>
-      <c r="E138">
+      <c r="E138" s="3">
         <v>-13739.07</v>
       </c>
     </row>
@@ -3930,7 +3931,7 @@
       <c r="D139" t="s">
         <v>149</v>
       </c>
-      <c r="E139">
+      <c r="E139" s="3">
         <v>-16550.78</v>
       </c>
     </row>
@@ -3947,7 +3948,7 @@
       <c r="D140" t="s">
         <v>150</v>
       </c>
-      <c r="E140">
+      <c r="E140" s="3">
         <v>-10664.59</v>
       </c>
     </row>
@@ -3964,7 +3965,7 @@
       <c r="D141" t="s">
         <v>151</v>
       </c>
-      <c r="E141">
+      <c r="E141" s="3">
         <v>4500</v>
       </c>
     </row>
@@ -3981,7 +3982,7 @@
       <c r="D142" t="s">
         <v>152</v>
       </c>
-      <c r="E142">
+      <c r="E142" s="3">
         <v>14800</v>
       </c>
     </row>
@@ -3998,7 +3999,7 @@
       <c r="D143" t="s">
         <v>70</v>
       </c>
-      <c r="E143">
+      <c r="E143" s="3">
         <v>-509</v>
       </c>
     </row>
@@ -4015,7 +4016,7 @@
       <c r="D144" t="s">
         <v>154</v>
       </c>
-      <c r="E144">
+      <c r="E144" s="3">
         <v>-9751.0499999999993</v>
       </c>
     </row>
@@ -4032,7 +4033,7 @@
       <c r="D145" t="s">
         <v>155</v>
       </c>
-      <c r="E145">
+      <c r="E145" s="3">
         <v>-8275.9699999999993</v>
       </c>
     </row>
@@ -4049,7 +4050,7 @@
       <c r="D146" t="s">
         <v>156</v>
       </c>
-      <c r="E146">
+      <c r="E146" s="3">
         <v>-9801.0400000000009</v>
       </c>
     </row>
@@ -4066,7 +4067,7 @@
       <c r="D147" t="s">
         <v>57</v>
       </c>
-      <c r="E147">
+      <c r="E147" s="3">
         <v>169612</v>
       </c>
     </row>
@@ -4083,7 +4084,7 @@
       <c r="D148" t="s">
         <v>157</v>
       </c>
-      <c r="E148">
+      <c r="E148" s="3">
         <v>3500</v>
       </c>
     </row>
@@ -4100,7 +4101,7 @@
       <c r="D149" t="s">
         <v>159</v>
       </c>
-      <c r="E149">
+      <c r="E149" s="3">
         <v>6800</v>
       </c>
     </row>
@@ -4117,7 +4118,7 @@
       <c r="D150" t="s">
         <v>161</v>
       </c>
-      <c r="E150">
+      <c r="E150" s="3">
         <v>7800</v>
       </c>
     </row>
@@ -4134,7 +4135,7 @@
       <c r="D151" t="s">
         <v>57</v>
       </c>
-      <c r="E151">
+      <c r="E151" s="3">
         <v>160000</v>
       </c>
     </row>
@@ -4151,7 +4152,7 @@
       <c r="D152" t="s">
         <v>162</v>
       </c>
-      <c r="E152">
+      <c r="E152" s="3">
         <v>-152000</v>
       </c>
     </row>
@@ -4168,7 +4169,7 @@
       <c r="D153" t="s">
         <v>57</v>
       </c>
-      <c r="E153">
+      <c r="E153" s="3">
         <v>181064.81</v>
       </c>
     </row>
@@ -4185,7 +4186,7 @@
       <c r="D154" t="s">
         <v>163</v>
       </c>
-      <c r="E154">
+      <c r="E154" s="3">
         <v>-63469.440000000002</v>
       </c>
     </row>
@@ -4202,7 +4203,7 @@
       <c r="D155" t="s">
         <v>164</v>
       </c>
-      <c r="E155">
+      <c r="E155" s="3">
         <v>-26078.27</v>
       </c>
     </row>
@@ -4219,7 +4220,7 @@
       <c r="D156" t="s">
         <v>165</v>
       </c>
-      <c r="E156">
+      <c r="E156" s="3">
         <v>-14735.71</v>
       </c>
     </row>
@@ -4236,7 +4237,7 @@
       <c r="D157" t="s">
         <v>166</v>
       </c>
-      <c r="E157">
+      <c r="E157" s="3">
         <v>-4260.6899999999996</v>
       </c>
     </row>
@@ -4253,7 +4254,7 @@
       <c r="D158" t="s">
         <v>167</v>
       </c>
-      <c r="E158">
+      <c r="E158" s="3">
         <v>-20404.080000000002</v>
       </c>
     </row>
@@ -4270,7 +4271,7 @@
       <c r="D159" t="s">
         <v>168</v>
       </c>
-      <c r="E159">
+      <c r="E159" s="3">
         <v>-16575.11</v>
       </c>
     </row>
@@ -4287,7 +4288,7 @@
       <c r="D160" t="s">
         <v>169</v>
       </c>
-      <c r="E160">
+      <c r="E160" s="3">
         <v>-8311.17</v>
       </c>
     </row>
@@ -4304,7 +4305,7 @@
       <c r="D161" t="s">
         <v>170</v>
       </c>
-      <c r="E161">
+      <c r="E161" s="3">
         <v>-4373.3</v>
       </c>
     </row>
@@ -4321,7 +4322,7 @@
       <c r="D162" t="s">
         <v>171</v>
       </c>
-      <c r="E162">
+      <c r="E162" s="3">
         <v>-5874.67</v>
       </c>
     </row>
@@ -4338,7 +4339,7 @@
       <c r="D163" t="s">
         <v>172</v>
       </c>
-      <c r="E163">
+      <c r="E163" s="3">
         <v>7600</v>
       </c>
     </row>
@@ -4355,7 +4356,7 @@
       <c r="D164" t="s">
         <v>57</v>
       </c>
-      <c r="E164">
+      <c r="E164" s="3">
         <v>46255</v>
       </c>
     </row>
@@ -4372,7 +4373,7 @@
       <c r="D165" t="s">
         <v>174</v>
       </c>
-      <c r="E165">
+      <c r="E165" s="3">
         <v>-71000</v>
       </c>
     </row>
@@ -4389,7 +4390,7 @@
       <c r="D166" t="s">
         <v>175</v>
       </c>
-      <c r="E166">
+      <c r="E166" s="3">
         <v>6300</v>
       </c>
     </row>
@@ -4406,7 +4407,7 @@
       <c r="D167" t="s">
         <v>177</v>
       </c>
-      <c r="E167">
+      <c r="E167" s="3">
         <v>13950</v>
       </c>
     </row>
@@ -4423,7 +4424,7 @@
       <c r="D168" t="s">
         <v>57</v>
       </c>
-      <c r="E168">
+      <c r="E168" s="3">
         <v>93778.74</v>
       </c>
     </row>
@@ -4440,7 +4441,7 @@
       <c r="D169" t="s">
         <v>57</v>
       </c>
-      <c r="E169">
+      <c r="E169" s="3">
         <v>41428.620000000003</v>
       </c>
     </row>
@@ -4457,7 +4458,7 @@
       <c r="D170" t="s">
         <v>178</v>
       </c>
-      <c r="E170">
+      <c r="E170" s="3">
         <v>-171851.18</v>
       </c>
     </row>
@@ -4474,7 +4475,7 @@
       <c r="D171" t="s">
         <v>179</v>
       </c>
-      <c r="E171">
+      <c r="E171" s="3">
         <v>-61714.22</v>
       </c>
     </row>
@@ -4491,7 +4492,7 @@
       <c r="D172" t="s">
         <v>180</v>
       </c>
-      <c r="E172">
+      <c r="E172" s="3">
         <v>-26107.95</v>
       </c>
     </row>
@@ -4508,7 +4509,7 @@
       <c r="D173" t="s">
         <v>181</v>
       </c>
-      <c r="E173">
+      <c r="E173" s="3">
         <v>-11424.04</v>
       </c>
     </row>
@@ -4525,7 +4526,7 @@
       <c r="D174" t="s">
         <v>182</v>
       </c>
-      <c r="E174">
+      <c r="E174" s="3">
         <v>-13481.88</v>
       </c>
     </row>
@@ -4542,7 +4543,7 @@
       <c r="D175" t="s">
         <v>183</v>
       </c>
-      <c r="E175">
+      <c r="E175" s="3">
         <v>-11676.11</v>
       </c>
     </row>
@@ -4559,7 +4560,7 @@
       <c r="D176" t="s">
         <v>184</v>
       </c>
-      <c r="E176">
+      <c r="E176" s="3">
         <v>-1749.83</v>
       </c>
     </row>
@@ -4576,7 +4577,7 @@
       <c r="D177" t="s">
         <v>185</v>
       </c>
-      <c r="E177">
+      <c r="E177" s="3">
         <v>18250</v>
       </c>
     </row>
@@ -4593,7 +4594,7 @@
       <c r="D178" t="s">
         <v>90</v>
       </c>
-      <c r="E178">
+      <c r="E178" s="3">
         <v>-179</v>
       </c>
     </row>
@@ -4610,7 +4611,7 @@
       <c r="D179" t="s">
         <v>89</v>
       </c>
-      <c r="E179">
+      <c r="E179" s="3">
         <v>-179</v>
       </c>
     </row>
@@ -4627,7 +4628,7 @@
       <c r="D180" t="s">
         <v>187</v>
       </c>
-      <c r="E180">
+      <c r="E180" s="3">
         <v>4750</v>
       </c>
     </row>
@@ -4644,7 +4645,7 @@
       <c r="D181" t="s">
         <v>57</v>
       </c>
-      <c r="E181">
+      <c r="E181" s="3">
         <v>84649.86</v>
       </c>
     </row>
@@ -4661,7 +4662,7 @@
       <c r="D182" t="s">
         <v>189</v>
       </c>
-      <c r="E182">
+      <c r="E182" s="3">
         <v>-29893.53</v>
       </c>
     </row>
@@ -4678,7 +4679,7 @@
       <c r="D183" t="s">
         <v>190</v>
       </c>
-      <c r="E183">
+      <c r="E183" s="3">
         <v>14350</v>
       </c>
     </row>
@@ -4695,7 +4696,7 @@
       <c r="D184" t="s">
         <v>57</v>
       </c>
-      <c r="E184">
+      <c r="E184" s="3">
         <v>188605.97</v>
       </c>
     </row>
@@ -4712,7 +4713,7 @@
       <c r="D185" t="s">
         <v>191</v>
       </c>
-      <c r="E185">
+      <c r="E185" s="3">
         <v>-135000</v>
       </c>
     </row>
@@ -4729,7 +4730,7 @@
       <c r="D186" t="s">
         <v>192</v>
       </c>
-      <c r="E186">
+      <c r="E186" s="3">
         <v>5450</v>
       </c>
     </row>
@@ -4746,7 +4747,7 @@
       <c r="D187" t="s">
         <v>194</v>
       </c>
-      <c r="E187">
+      <c r="E187" s="3">
         <v>6550</v>
       </c>
     </row>
@@ -4763,7 +4764,7 @@
       <c r="D188" t="s">
         <v>57</v>
       </c>
-      <c r="E188">
+      <c r="E188" s="3">
         <v>115315.88</v>
       </c>
     </row>
@@ -4780,7 +4781,7 @@
       <c r="D189" t="s">
         <v>195</v>
       </c>
-      <c r="E189">
+      <c r="E189" s="3">
         <v>-15000</v>
       </c>
     </row>
@@ -4797,7 +4798,7 @@
       <c r="D190" t="s">
         <v>196</v>
       </c>
-      <c r="E190">
+      <c r="E190" s="3">
         <v>-24000</v>
       </c>
     </row>
@@ -4814,7 +4815,7 @@
       <c r="D191" t="s">
         <v>120</v>
       </c>
-      <c r="E191">
+      <c r="E191" s="3">
         <v>-138016.76</v>
       </c>
     </row>
@@ -4831,7 +4832,7 @@
       <c r="D192" t="s">
         <v>57</v>
       </c>
-      <c r="E192">
+      <c r="E192" s="3">
         <v>65714.33</v>
       </c>
     </row>
@@ -4848,7 +4849,7 @@
       <c r="D193" t="s">
         <v>197</v>
       </c>
-      <c r="E193">
+      <c r="E193" s="3">
         <v>-74863.600000000006</v>
       </c>
     </row>
@@ -4865,7 +4866,7 @@
       <c r="D194" t="s">
         <v>198</v>
       </c>
-      <c r="E194">
+      <c r="E194" s="3">
         <v>-56071.34</v>
       </c>
     </row>
@@ -4882,7 +4883,7 @@
       <c r="D195" t="s">
         <v>199</v>
       </c>
-      <c r="E195">
+      <c r="E195" s="3">
         <v>-20456.54</v>
       </c>
     </row>
@@ -4899,7 +4900,7 @@
       <c r="D196" t="s">
         <v>57</v>
       </c>
-      <c r="E196">
+      <c r="E196" s="3">
         <v>54630.720000000001</v>
       </c>
     </row>
@@ -4916,7 +4917,7 @@
       <c r="D197" t="s">
         <v>200</v>
       </c>
-      <c r="E197">
+      <c r="E197" s="3">
         <v>8700</v>
       </c>
     </row>
@@ -4933,7 +4934,7 @@
       <c r="D198" t="s">
         <v>57</v>
       </c>
-      <c r="E198">
+      <c r="E198" s="3">
         <v>66895.23</v>
       </c>
     </row>
@@ -4950,7 +4951,7 @@
       <c r="D199" t="s">
         <v>57</v>
       </c>
-      <c r="E199">
+      <c r="E199" s="3">
         <v>56950.25</v>
       </c>
     </row>
@@ -4967,7 +4968,7 @@
       <c r="D200" t="s">
         <v>201</v>
       </c>
-      <c r="E200">
+      <c r="E200" s="3">
         <v>-28829.41</v>
       </c>
     </row>
@@ -4984,7 +4985,7 @@
       <c r="D201" t="s">
         <v>202</v>
       </c>
-      <c r="E201">
+      <c r="E201" s="3">
         <v>-18550.349999999999</v>
       </c>
     </row>
@@ -5001,7 +5002,7 @@
       <c r="D202" t="s">
         <v>204</v>
       </c>
-      <c r="E202">
+      <c r="E202" s="3">
         <v>9700</v>
       </c>
     </row>
@@ -5018,7 +5019,7 @@
       <c r="D203" t="s">
         <v>205</v>
       </c>
-      <c r="E203">
+      <c r="E203" s="3">
         <v>4850</v>
       </c>
     </row>
@@ -5035,7 +5036,7 @@
       <c r="D204" t="s">
         <v>207</v>
       </c>
-      <c r="E204">
+      <c r="E204" s="3">
         <v>2900</v>
       </c>
     </row>
@@ -5052,7 +5053,7 @@
       <c r="D205" t="s">
         <v>99</v>
       </c>
-      <c r="E205">
+      <c r="E205" s="3">
         <v>-60460.2</v>
       </c>
     </row>
@@ -5069,7 +5070,7 @@
       <c r="D206" t="s">
         <v>208</v>
       </c>
-      <c r="E206">
+      <c r="E206" s="3">
         <v>-33149.42</v>
       </c>
     </row>
@@ -5086,7 +5087,7 @@
       <c r="D207" t="s">
         <v>210</v>
       </c>
-      <c r="E207">
+      <c r="E207" s="3">
         <v>-13370.34</v>
       </c>
     </row>
@@ -5103,7 +5104,7 @@
       <c r="D208" t="s">
         <v>211</v>
       </c>
-      <c r="E208">
+      <c r="E208" s="3">
         <v>-15426.29</v>
       </c>
     </row>
@@ -5120,7 +5121,7 @@
       <c r="D209" t="s">
         <v>212</v>
       </c>
-      <c r="E209">
+      <c r="E209" s="3">
         <v>-28192.29</v>
       </c>
     </row>
@@ -5137,7 +5138,7 @@
       <c r="D210" t="s">
         <v>57</v>
       </c>
-      <c r="E210">
+      <c r="E210" s="3">
         <v>169519.16</v>
       </c>
     </row>
@@ -5154,7 +5155,7 @@
       <c r="D211" t="s">
         <v>214</v>
       </c>
-      <c r="E211">
+      <c r="E211" s="3">
         <v>9200</v>
       </c>
     </row>
@@ -5171,7 +5172,7 @@
       <c r="D212" t="s">
         <v>57</v>
       </c>
-      <c r="E212">
+      <c r="E212" s="3">
         <v>33567.5</v>
       </c>
     </row>
@@ -5188,7 +5189,7 @@
       <c r="D213" t="s">
         <v>57</v>
       </c>
-      <c r="E213">
+      <c r="E213" s="3">
         <v>69694.880000000005</v>
       </c>
     </row>
@@ -5205,7 +5206,7 @@
       <c r="D214" t="s">
         <v>121</v>
       </c>
-      <c r="E214">
+      <c r="E214" s="3">
         <v>-8554</v>
       </c>
     </row>
@@ -5222,7 +5223,7 @@
       <c r="D215" t="s">
         <v>216</v>
       </c>
-      <c r="E215">
+      <c r="E215" s="3">
         <v>-258930.95</v>
       </c>
     </row>
@@ -5239,7 +5240,7 @@
       <c r="D216" t="s">
         <v>217</v>
       </c>
-      <c r="E216">
+      <c r="E216" s="3">
         <v>14800</v>
       </c>
     </row>
@@ -5256,7 +5257,7 @@
       <c r="D217" t="s">
         <v>57</v>
       </c>
-      <c r="E217">
+      <c r="E217" s="3">
         <v>39770</v>
       </c>
     </row>
@@ -5273,7 +5274,7 @@
       <c r="D218" t="s">
         <v>219</v>
       </c>
-      <c r="E218">
+      <c r="E218" s="3">
         <v>-20622.419999999998</v>
       </c>
     </row>
@@ -5290,7 +5291,7 @@
       <c r="D219" t="s">
         <v>220</v>
       </c>
-      <c r="E219">
+      <c r="E219" s="3">
         <v>-13312.31</v>
       </c>
     </row>
@@ -5307,7 +5308,7 @@
       <c r="D220" t="s">
         <v>221</v>
       </c>
-      <c r="E220">
+      <c r="E220" s="3">
         <v>-8616.0400000000009</v>
       </c>
     </row>
@@ -5324,7 +5325,7 @@
       <c r="D221" t="s">
         <v>222</v>
       </c>
-      <c r="E221">
+      <c r="E221" s="3">
         <v>14450</v>
       </c>
     </row>
@@ -5341,7 +5342,7 @@
       <c r="D222" t="s">
         <v>57</v>
       </c>
-      <c r="E222">
+      <c r="E222" s="3">
         <v>36661.72</v>
       </c>
     </row>
@@ -5358,7 +5359,7 @@
       <c r="D223" t="s">
         <v>224</v>
       </c>
-      <c r="E223">
+      <c r="E223" s="3">
         <v>-101000</v>
       </c>
     </row>
@@ -5375,7 +5376,7 @@
       <c r="D224" t="s">
         <v>225</v>
       </c>
-      <c r="E224">
+      <c r="E224" s="3">
         <v>-1650</v>
       </c>
     </row>
@@ -5392,7 +5393,7 @@
       <c r="D225" t="s">
         <v>57</v>
       </c>
-      <c r="E225">
+      <c r="E225" s="3">
         <v>60770.73</v>
       </c>
     </row>
@@ -5409,7 +5410,7 @@
       <c r="D226" t="s">
         <v>227</v>
       </c>
-      <c r="E226">
+      <c r="E226" s="3">
         <v>8150</v>
       </c>
     </row>
@@ -5426,7 +5427,7 @@
       <c r="D227" t="s">
         <v>228</v>
       </c>
-      <c r="E227">
+      <c r="E227" s="3">
         <v>-23723.22</v>
       </c>
     </row>
@@ -5443,7 +5444,7 @@
       <c r="D228" t="s">
         <v>229</v>
       </c>
-      <c r="E228">
+      <c r="E228" s="3">
         <v>-55824.43</v>
       </c>
     </row>
@@ -5460,7 +5461,7 @@
       <c r="D229" t="s">
         <v>230</v>
       </c>
-      <c r="E229">
+      <c r="E229" s="3">
         <v>-44588.2</v>
       </c>
     </row>
@@ -5477,7 +5478,7 @@
       <c r="D230" t="s">
         <v>231</v>
       </c>
-      <c r="E230">
+      <c r="E230" s="3">
         <v>-5038.3900000000003</v>
       </c>
     </row>
@@ -5494,7 +5495,7 @@
       <c r="D231" t="s">
         <v>53</v>
       </c>
-      <c r="E231">
+      <c r="E231" s="3">
         <v>64765</v>
       </c>
     </row>
@@ -5511,7 +5512,7 @@
       <c r="D232" t="s">
         <v>232</v>
       </c>
-      <c r="E232">
+      <c r="E232" s="3">
         <v>-13479.42</v>
       </c>
     </row>
@@ -5528,7 +5529,7 @@
       <c r="D233" t="s">
         <v>233</v>
       </c>
-      <c r="E233">
+      <c r="E233" s="3">
         <v>-11250</v>
       </c>
     </row>
@@ -5545,7 +5546,7 @@
       <c r="D234" t="s">
         <v>57</v>
       </c>
-      <c r="E234">
+      <c r="E234" s="3">
         <v>60359.35</v>
       </c>
     </row>
@@ -5562,7 +5563,7 @@
       <c r="D235" t="s">
         <v>236</v>
       </c>
-      <c r="E235">
+      <c r="E235" s="3">
         <v>16000</v>
       </c>
     </row>
@@ -5579,7 +5580,7 @@
       <c r="D236" t="s">
         <v>57</v>
       </c>
-      <c r="E236">
+      <c r="E236" s="3">
         <v>38840</v>
       </c>
     </row>
@@ -5596,7 +5597,7 @@
       <c r="D237" t="s">
         <v>122</v>
       </c>
-      <c r="E237">
+      <c r="E237" s="3">
         <v>30000</v>
       </c>
     </row>
@@ -5613,7 +5614,7 @@
       <c r="D238" t="s">
         <v>57</v>
       </c>
-      <c r="E238">
+      <c r="E238" s="3">
         <v>42500</v>
       </c>
     </row>
@@ -5630,7 +5631,7 @@
       <c r="D239" t="s">
         <v>237</v>
       </c>
-      <c r="E239">
+      <c r="E239" s="3">
         <v>-224094.71</v>
       </c>
     </row>
@@ -5647,7 +5648,7 @@
       <c r="D240" t="s">
         <v>238</v>
       </c>
-      <c r="E240">
+      <c r="E240" s="3">
         <v>4000</v>
       </c>
     </row>
@@ -5664,7 +5665,7 @@
       <c r="D241" t="s">
         <v>57</v>
       </c>
-      <c r="E241">
+      <c r="E241" s="3">
         <v>91449.94</v>
       </c>
     </row>
@@ -5681,7 +5682,7 @@
       <c r="D242" t="s">
         <v>240</v>
       </c>
-      <c r="E242">
+      <c r="E242" s="3">
         <v>5300</v>
       </c>
     </row>
@@ -5698,7 +5699,7 @@
       <c r="D243" t="s">
         <v>242</v>
       </c>
-      <c r="E243">
+      <c r="E243" s="3">
         <v>-30000</v>
       </c>
     </row>
@@ -5715,7 +5716,7 @@
       <c r="D244" t="s">
         <v>70</v>
       </c>
-      <c r="E244">
+      <c r="E244" s="3">
         <v>-509</v>
       </c>
     </row>
@@ -5732,7 +5733,7 @@
       <c r="D245" t="s">
         <v>57</v>
       </c>
-      <c r="E245">
+      <c r="E245" s="3">
         <v>83774.539999999994</v>
       </c>
     </row>
@@ -5749,7 +5750,7 @@
       <c r="D246" t="s">
         <v>244</v>
       </c>
-      <c r="E246">
+      <c r="E246" s="3">
         <v>8500</v>
       </c>
     </row>
@@ -5766,7 +5767,7 @@
       <c r="D247" t="s">
         <v>245</v>
       </c>
-      <c r="E247">
+      <c r="E247" s="3">
         <v>-34648.559999999998</v>
       </c>
     </row>
@@ -5783,7 +5784,7 @@
       <c r="D248" t="s">
         <v>246</v>
       </c>
-      <c r="E248">
+      <c r="E248" s="3">
         <v>-10528.75</v>
       </c>
     </row>
@@ -5800,7 +5801,7 @@
       <c r="D249" t="s">
         <v>247</v>
       </c>
-      <c r="E249">
+      <c r="E249" s="3">
         <v>-6144.7</v>
       </c>
     </row>
@@ -5817,7 +5818,7 @@
       <c r="D250" t="s">
         <v>90</v>
       </c>
-      <c r="E250">
+      <c r="E250" s="3">
         <v>-239</v>
       </c>
     </row>
@@ -5834,7 +5835,7 @@
       <c r="D251" t="s">
         <v>89</v>
       </c>
-      <c r="E251">
+      <c r="E251" s="3">
         <v>-239</v>
       </c>
     </row>
@@ -5851,7 +5852,7 @@
       <c r="D252" t="s">
         <v>249</v>
       </c>
-      <c r="E252">
+      <c r="E252" s="3">
         <v>5900</v>
       </c>
     </row>
@@ -5868,7 +5869,7 @@
       <c r="D253" t="s">
         <v>57</v>
       </c>
-      <c r="E253">
+      <c r="E253" s="3">
         <v>120000</v>
       </c>
     </row>
@@ -5885,7 +5886,7 @@
       <c r="D254" t="s">
         <v>251</v>
       </c>
-      <c r="E254">
+      <c r="E254" s="3">
         <v>7200</v>
       </c>
     </row>
@@ -5902,7 +5903,7 @@
       <c r="D255" t="s">
         <v>253</v>
       </c>
-      <c r="E255">
+      <c r="E255" s="3">
         <v>3550</v>
       </c>
     </row>
@@ -5919,7 +5920,7 @@
       <c r="D256" t="s">
         <v>254</v>
       </c>
-      <c r="E256">
+      <c r="E256" s="3">
         <v>-59048.73</v>
       </c>
     </row>
@@ -5936,7 +5937,7 @@
       <c r="D257" t="s">
         <v>255</v>
       </c>
-      <c r="E257">
+      <c r="E257" s="3">
         <v>-19296.84</v>
       </c>
     </row>
@@ -5953,7 +5954,7 @@
       <c r="D258" t="s">
         <v>256</v>
       </c>
-      <c r="E258">
+      <c r="E258" s="3">
         <v>-31232.91</v>
       </c>
     </row>
@@ -5970,7 +5971,7 @@
       <c r="D259" t="s">
         <v>257</v>
       </c>
-      <c r="E259">
+      <c r="E259" s="3">
         <v>-16240.37</v>
       </c>
     </row>
@@ -5987,7 +5988,7 @@
       <c r="D260" t="s">
         <v>57</v>
       </c>
-      <c r="E260">
+      <c r="E260" s="3">
         <v>299434.05</v>
       </c>
     </row>
@@ -6004,7 +6005,7 @@
       <c r="D261" t="s">
         <v>258</v>
       </c>
-      <c r="E261">
+      <c r="E261" s="3">
         <v>-17317.330000000002</v>
       </c>
     </row>
@@ -6021,7 +6022,7 @@
       <c r="D262" t="s">
         <v>259</v>
       </c>
-      <c r="E262">
+      <c r="E262" s="3">
         <v>-9217.77</v>
       </c>
     </row>
@@ -6038,7 +6039,7 @@
       <c r="D263" t="s">
         <v>260</v>
       </c>
-      <c r="E263">
+      <c r="E263" s="3">
         <v>-42549.51</v>
       </c>
     </row>
@@ -6055,7 +6056,7 @@
       <c r="D264" t="s">
         <v>261</v>
       </c>
-      <c r="E264">
+      <c r="E264" s="3">
         <v>-22972.83</v>
       </c>
     </row>
@@ -6072,7 +6073,7 @@
       <c r="D265" t="s">
         <v>262</v>
       </c>
-      <c r="E265">
+      <c r="E265" s="3">
         <v>-7749.23</v>
       </c>
     </row>
@@ -6089,7 +6090,7 @@
       <c r="D266" t="s">
         <v>263</v>
       </c>
-      <c r="E266">
+      <c r="E266" s="3">
         <v>-171479.76</v>
       </c>
     </row>
@@ -6106,7 +6107,7 @@
       <c r="D267" t="s">
         <v>264</v>
       </c>
-      <c r="E267">
+      <c r="E267" s="3">
         <v>-41000</v>
       </c>
     </row>
@@ -6123,7 +6124,7 @@
       <c r="D268" t="s">
         <v>265</v>
       </c>
-      <c r="E268">
+      <c r="E268" s="3">
         <v>4200</v>
       </c>
     </row>
@@ -6140,7 +6141,7 @@
       <c r="D269" t="s">
         <v>57</v>
       </c>
-      <c r="E269">
+      <c r="E269" s="3">
         <v>47535</v>
       </c>
     </row>
@@ -6157,7 +6158,7 @@
       <c r="D270" t="s">
         <v>267</v>
       </c>
-      <c r="E270">
+      <c r="E270" s="3">
         <v>13000</v>
       </c>
     </row>
@@ -6174,7 +6175,7 @@
       <c r="D271" t="s">
         <v>269</v>
       </c>
-      <c r="E271">
+      <c r="E271" s="3">
         <v>4900</v>
       </c>
     </row>
@@ -6191,7 +6192,7 @@
       <c r="D272" t="s">
         <v>271</v>
       </c>
-      <c r="E272">
+      <c r="E272" s="3">
         <v>9400</v>
       </c>
     </row>
@@ -6208,7 +6209,7 @@
       <c r="D273" t="s">
         <v>57</v>
       </c>
-      <c r="E273">
+      <c r="E273" s="3">
         <v>154825.82</v>
       </c>
     </row>
@@ -6225,7 +6226,7 @@
       <c r="D274" t="s">
         <v>272</v>
       </c>
-      <c r="E274">
+      <c r="E274" s="3">
         <v>-51589.74</v>
       </c>
     </row>
@@ -6242,7 +6243,7 @@
       <c r="D275" t="s">
         <v>273</v>
       </c>
-      <c r="E275">
+      <c r="E275" s="3">
         <v>-18438.439999999999</v>
       </c>
     </row>
@@ -6259,7 +6260,7 @@
       <c r="D276" t="s">
         <v>274</v>
       </c>
-      <c r="E276">
+      <c r="E276" s="3">
         <v>-18543.78</v>
       </c>
     </row>
@@ -6276,7 +6277,7 @@
       <c r="D277" t="s">
         <v>275</v>
       </c>
-      <c r="E277">
+      <c r="E277" s="3">
         <v>-40628.339999999997</v>
       </c>
     </row>
@@ -6293,7 +6294,7 @@
       <c r="D278" t="s">
         <v>276</v>
       </c>
-      <c r="E278">
+      <c r="E278" s="3">
         <v>-6383.71</v>
       </c>
     </row>
@@ -6310,7 +6311,7 @@
       <c r="D279" t="s">
         <v>277</v>
       </c>
-      <c r="E279">
+      <c r="E279" s="3">
         <v>-5345.43</v>
       </c>
     </row>
@@ -6327,7 +6328,7 @@
       <c r="D280" t="s">
         <v>278</v>
       </c>
-      <c r="E280">
+      <c r="E280" s="3">
         <v>-10249.08</v>
       </c>
     </row>
@@ -6344,7 +6345,7 @@
       <c r="D281" t="s">
         <v>279</v>
       </c>
-      <c r="E281">
+      <c r="E281" s="3">
         <v>-7678.53</v>
       </c>
     </row>
@@ -6361,7 +6362,7 @@
       <c r="D282" t="s">
         <v>280</v>
       </c>
-      <c r="E282">
+      <c r="E282" s="3">
         <v>-1893.23</v>
       </c>
     </row>
@@ -6378,7 +6379,7 @@
       <c r="D283" t="s">
         <v>282</v>
       </c>
-      <c r="E283">
+      <c r="E283" s="3">
         <v>8500</v>
       </c>
     </row>
@@ -6395,7 +6396,7 @@
       <c r="D284" t="s">
         <v>57</v>
       </c>
-      <c r="E284">
+      <c r="E284" s="3">
         <v>81987.820000000007</v>
       </c>
     </row>
@@ -6412,7 +6413,7 @@
       <c r="D285" t="s">
         <v>284</v>
       </c>
-      <c r="E285">
+      <c r="E285" s="3">
         <v>10000</v>
       </c>
     </row>
@@ -6429,7 +6430,7 @@
       <c r="D286" t="s">
         <v>286</v>
       </c>
-      <c r="E286">
+      <c r="E286" s="3">
         <v>6300</v>
       </c>
     </row>
@@ -6446,7 +6447,7 @@
       <c r="D287" t="s">
         <v>288</v>
       </c>
-      <c r="E287">
+      <c r="E287" s="3">
         <v>7450</v>
       </c>
     </row>
@@ -6463,7 +6464,7 @@
       <c r="D288" t="s">
         <v>224</v>
       </c>
-      <c r="E288">
+      <c r="E288" s="3">
         <v>-19500</v>
       </c>
     </row>
@@ -6480,7 +6481,7 @@
       <c r="D289" t="s">
         <v>120</v>
       </c>
-      <c r="E289">
+      <c r="E289" s="3">
         <v>-142209.63</v>
       </c>
     </row>
@@ -6497,7 +6498,7 @@
       <c r="D290" t="s">
         <v>290</v>
       </c>
-      <c r="E290">
+      <c r="E290" s="3">
         <v>-16900</v>
       </c>
     </row>
@@ -6514,7 +6515,7 @@
       <c r="D291" t="s">
         <v>57</v>
       </c>
-      <c r="E291">
+      <c r="E291" s="3">
         <v>394323.43</v>
       </c>
     </row>
@@ -6531,7 +6532,7 @@
       <c r="D292" t="s">
         <v>291</v>
       </c>
-      <c r="E292">
+      <c r="E292" s="3">
         <v>-132000</v>
       </c>
     </row>
@@ -6548,7 +6549,7 @@
       <c r="D293" t="s">
         <v>292</v>
       </c>
-      <c r="E293">
+      <c r="E293" s="3">
         <v>-1337.2</v>
       </c>
     </row>
@@ -6565,7 +6566,7 @@
       <c r="D294" t="s">
         <v>294</v>
       </c>
-      <c r="E294">
+      <c r="E294" s="3">
         <v>14600</v>
       </c>
     </row>
@@ -6582,7 +6583,7 @@
       <c r="D295" t="s">
         <v>295</v>
       </c>
-      <c r="E295">
+      <c r="E295" s="3">
         <v>9700</v>
       </c>
     </row>
@@ -6599,7 +6600,7 @@
       <c r="D296" t="s">
         <v>121</v>
       </c>
-      <c r="E296">
+      <c r="E296" s="3">
         <v>-7310</v>
       </c>
     </row>
@@ -6616,7 +6617,7 @@
       <c r="D297" t="s">
         <v>297</v>
       </c>
-      <c r="E297">
+      <c r="E297" s="3">
         <v>-47335.23</v>
       </c>
     </row>
@@ -6633,7 +6634,7 @@
       <c r="D298" t="s">
         <v>298</v>
       </c>
-      <c r="E298">
+      <c r="E298" s="3">
         <v>-8456.23</v>
       </c>
     </row>
@@ -6650,7 +6651,7 @@
       <c r="D299" t="s">
         <v>299</v>
       </c>
-      <c r="E299">
+      <c r="E299" s="3">
         <v>-16118.47</v>
       </c>
     </row>
@@ -6667,7 +6668,7 @@
       <c r="D300" t="s">
         <v>300</v>
       </c>
-      <c r="E300">
+      <c r="E300" s="3">
         <v>-30503.03</v>
       </c>
     </row>
@@ -6684,7 +6685,7 @@
       <c r="D301" t="s">
         <v>301</v>
       </c>
-      <c r="E301">
+      <c r="E301" s="3">
         <v>-5848.41</v>
       </c>
     </row>
@@ -6701,7 +6702,7 @@
       <c r="D302" t="s">
         <v>302</v>
       </c>
-      <c r="E302">
+      <c r="E302" s="3">
         <v>-17330.28</v>
       </c>
     </row>
@@ -6718,7 +6719,7 @@
       <c r="D303" t="s">
         <v>57</v>
       </c>
-      <c r="E303">
+      <c r="E303" s="3">
         <v>195672.17</v>
       </c>
     </row>
@@ -6735,7 +6736,7 @@
       <c r="D304" t="s">
         <v>304</v>
       </c>
-      <c r="E304">
+      <c r="E304" s="3">
         <v>-24500.39</v>
       </c>
     </row>
@@ -6752,7 +6753,7 @@
       <c r="D305" t="s">
         <v>305</v>
       </c>
-      <c r="E305">
+      <c r="E305" s="3">
         <v>-17802.47</v>
       </c>
     </row>
@@ -6769,7 +6770,7 @@
       <c r="D306" t="s">
         <v>306</v>
       </c>
-      <c r="E306">
+      <c r="E306" s="3">
         <v>-19421.689999999999</v>
       </c>
     </row>
@@ -6786,7 +6787,7 @@
       <c r="D307" t="s">
         <v>307</v>
       </c>
-      <c r="E307">
+      <c r="E307" s="3">
         <v>-4694.83</v>
       </c>
     </row>
@@ -6803,7 +6804,7 @@
       <c r="D308" t="s">
         <v>308</v>
       </c>
-      <c r="E308">
+      <c r="E308" s="3">
         <v>-293138.03999999998</v>
       </c>
     </row>
@@ -6820,7 +6821,7 @@
       <c r="D309" t="s">
         <v>309</v>
       </c>
-      <c r="E309">
+      <c r="E309" s="3">
         <v>13700</v>
       </c>
     </row>
@@ -6837,7 +6838,7 @@
       <c r="D310" t="s">
         <v>310</v>
       </c>
-      <c r="E310">
+      <c r="E310" s="3">
         <v>-4191</v>
       </c>
     </row>
@@ -6854,7 +6855,7 @@
       <c r="D311" t="s">
         <v>311</v>
       </c>
-      <c r="E311">
+      <c r="E311" s="3">
         <v>-4255</v>
       </c>
     </row>
@@ -6871,7 +6872,7 @@
       <c r="D312" t="s">
         <v>312</v>
       </c>
-      <c r="E312">
+      <c r="E312" s="3">
         <v>-3889</v>
       </c>
     </row>
@@ -6888,7 +6889,7 @@
       <c r="D313" t="s">
         <v>313</v>
       </c>
-      <c r="E313">
+      <c r="E313" s="3">
         <v>-3672</v>
       </c>
     </row>
@@ -6905,7 +6906,7 @@
       <c r="D314" t="s">
         <v>314</v>
       </c>
-      <c r="E314">
+      <c r="E314" s="3">
         <v>-6505</v>
       </c>
     </row>
@@ -6922,7 +6923,7 @@
       <c r="D315" t="s">
         <v>315</v>
       </c>
-      <c r="E315">
+      <c r="E315" s="3">
         <v>-3884</v>
       </c>
     </row>
@@ -6939,7 +6940,7 @@
       <c r="D316" t="s">
         <v>317</v>
       </c>
-      <c r="E316">
+      <c r="E316" s="3">
         <v>6100</v>
       </c>
     </row>
@@ -6956,7 +6957,7 @@
       <c r="D317" t="s">
         <v>319</v>
       </c>
-      <c r="E317">
+      <c r="E317" s="3">
         <v>9400</v>
       </c>
     </row>
@@ -6973,7 +6974,7 @@
       <c r="D318" t="s">
         <v>57</v>
       </c>
-      <c r="E318">
+      <c r="E318" s="3">
         <v>71325</v>
       </c>
     </row>
@@ -6990,7 +6991,7 @@
       <c r="D319" t="s">
         <v>320</v>
       </c>
-      <c r="E319">
+      <c r="E319" s="3">
         <v>-2507.34</v>
       </c>
     </row>
@@ -7007,7 +7008,7 @@
       <c r="D320" t="s">
         <v>321</v>
       </c>
-      <c r="E320">
+      <c r="E320" s="3">
         <v>-9936.3799999999992</v>
       </c>
     </row>
@@ -7024,7 +7025,7 @@
       <c r="D321" t="s">
         <v>322</v>
       </c>
-      <c r="E321">
+      <c r="E321" s="3">
         <v>-12125.55</v>
       </c>
     </row>
@@ -7041,7 +7042,7 @@
       <c r="D322" t="s">
         <v>324</v>
       </c>
-      <c r="E322">
+      <c r="E322" s="3">
         <v>-1516.66</v>
       </c>
     </row>
@@ -7058,7 +7059,7 @@
       <c r="D323" t="s">
         <v>325</v>
       </c>
-      <c r="E323">
+      <c r="E323" s="3">
         <v>-12349</v>
       </c>
     </row>
@@ -7075,7 +7076,7 @@
       <c r="D324" t="s">
         <v>326</v>
       </c>
-      <c r="E324">
+      <c r="E324" s="3">
         <v>-9060</v>
       </c>
     </row>
@@ -7092,7 +7093,7 @@
       <c r="D325" t="s">
         <v>57</v>
       </c>
-      <c r="E325">
+      <c r="E325" s="3">
         <v>33608.82</v>
       </c>
     </row>
@@ -7109,7 +7110,7 @@
       <c r="D326" t="s">
         <v>327</v>
       </c>
-      <c r="E326">
+      <c r="E326" s="3">
         <v>-5400</v>
       </c>
     </row>
@@ -7126,7 +7127,7 @@
       <c r="D327" t="s">
         <v>328</v>
       </c>
-      <c r="E327">
+      <c r="E327" s="3">
         <v>-53856.55</v>
       </c>
     </row>
@@ -7143,7 +7144,7 @@
       <c r="D328" t="s">
         <v>329</v>
       </c>
-      <c r="E328">
+      <c r="E328" s="3">
         <v>-43447.41</v>
       </c>
     </row>
@@ -7160,7 +7161,7 @@
       <c r="D329" t="s">
         <v>330</v>
       </c>
-      <c r="E329">
+      <c r="E329" s="3">
         <v>-31918.97</v>
       </c>
     </row>
@@ -7177,7 +7178,7 @@
       <c r="D330" t="s">
         <v>331</v>
       </c>
-      <c r="E330">
+      <c r="E330" s="3">
         <v>-18316.43</v>
       </c>
     </row>
@@ -7194,7 +7195,7 @@
       <c r="D331" t="s">
         <v>332</v>
       </c>
-      <c r="E331">
+      <c r="E331" s="3">
         <v>-5345.43</v>
       </c>
     </row>
@@ -7211,7 +7212,7 @@
       <c r="D332" t="s">
         <v>333</v>
       </c>
-      <c r="E332">
+      <c r="E332" s="3">
         <v>-2456.83</v>
       </c>
     </row>
@@ -7228,7 +7229,7 @@
       <c r="D333" t="s">
         <v>335</v>
       </c>
-      <c r="E333">
+      <c r="E333" s="3">
         <v>6400</v>
       </c>
     </row>
@@ -7245,7 +7246,7 @@
       <c r="D334" t="s">
         <v>57</v>
       </c>
-      <c r="E334">
+      <c r="E334" s="3">
         <v>138263.45000000001</v>
       </c>
     </row>
@@ -7262,7 +7263,7 @@
       <c r="D335" t="s">
         <v>337</v>
       </c>
-      <c r="E335">
+      <c r="E335" s="3">
         <v>-62664.01</v>
       </c>
     </row>
@@ -7279,7 +7280,7 @@
       <c r="D336" t="s">
         <v>338</v>
       </c>
-      <c r="E336">
+      <c r="E336" s="3">
         <v>12200</v>
       </c>
     </row>
@@ -7296,7 +7297,7 @@
       <c r="D337" t="s">
         <v>57</v>
       </c>
-      <c r="E337">
+      <c r="E337" s="3">
         <v>39529.040000000001</v>
       </c>
     </row>
@@ -7313,7 +7314,7 @@
       <c r="D338" t="s">
         <v>57</v>
       </c>
-      <c r="E338">
+      <c r="E338" s="3">
         <v>42170</v>
       </c>
     </row>
@@ -7330,7 +7331,7 @@
       <c r="D339" t="s">
         <v>341</v>
       </c>
-      <c r="E339">
+      <c r="E339" s="3">
         <v>13900</v>
       </c>
     </row>
@@ -7347,7 +7348,7 @@
       <c r="D340" t="s">
         <v>343</v>
       </c>
-      <c r="E340" s="2">
+      <c r="E340" s="3">
         <v>-188605.97</v>
       </c>
     </row>
@@ -7364,7 +7365,7 @@
       <c r="D341" t="s">
         <v>344</v>
       </c>
-      <c r="E341" s="2">
+      <c r="E341" s="3">
         <v>1225</v>
       </c>
     </row>
@@ -7381,7 +7382,7 @@
       <c r="D342" t="s">
         <v>345</v>
       </c>
-      <c r="E342" s="2">
+      <c r="E342" s="3">
         <v>-23.28</v>
       </c>
     </row>
@@ -7398,7 +7399,7 @@
       <c r="D343" t="s">
         <v>346</v>
       </c>
-      <c r="E343" s="2">
+      <c r="E343" s="3">
         <v>-1.1599999999999999</v>
       </c>
     </row>
@@ -7415,7 +7416,7 @@
       <c r="D344" t="s">
         <v>347</v>
       </c>
-      <c r="E344" s="2">
+      <c r="E344" s="3">
         <v>1440</v>
       </c>
     </row>
@@ -7432,7 +7433,7 @@
       <c r="D345" t="s">
         <v>348</v>
       </c>
-      <c r="E345" s="2">
+      <c r="E345" s="3">
         <v>3770</v>
       </c>
     </row>
@@ -7449,7 +7450,7 @@
       <c r="D346" t="s">
         <v>349</v>
       </c>
-      <c r="E346" s="2">
+      <c r="E346" s="3">
         <v>35945</v>
       </c>
     </row>
@@ -7466,7 +7467,7 @@
       <c r="D347" t="s">
         <v>350</v>
       </c>
-      <c r="E347" s="2">
+      <c r="E347" s="3">
         <v>20542</v>
       </c>
     </row>
@@ -7483,7 +7484,7 @@
       <c r="D348" t="s">
         <v>351</v>
       </c>
-      <c r="E348" s="2">
+      <c r="E348" s="3">
         <v>1260</v>
       </c>
     </row>
@@ -7500,7 +7501,7 @@
       <c r="D349" t="s">
         <v>347</v>
       </c>
-      <c r="E349" s="2">
+      <c r="E349" s="3">
         <v>690</v>
       </c>
     </row>
@@ -7517,7 +7518,7 @@
       <c r="D350" t="s">
         <v>348</v>
       </c>
-      <c r="E350" s="2">
+      <c r="E350" s="3">
         <v>1290</v>
       </c>
     </row>
@@ -7534,7 +7535,7 @@
       <c r="D351" t="s">
         <v>349</v>
       </c>
-      <c r="E351" s="2">
+      <c r="E351" s="3">
         <v>28025</v>
       </c>
     </row>
@@ -7551,7 +7552,7 @@
       <c r="D352" t="s">
         <v>350</v>
       </c>
-      <c r="E352" s="2">
+      <c r="E352" s="3">
         <v>19602.5</v>
       </c>
     </row>
@@ -7568,7 +7569,7 @@
       <c r="D353" t="s">
         <v>351</v>
       </c>
-      <c r="E353" s="2">
+      <c r="E353" s="3">
         <v>1100</v>
       </c>
     </row>
@@ -7585,7 +7586,7 @@
       <c r="D354" t="s">
         <v>344</v>
       </c>
-      <c r="E354" s="2">
+      <c r="E354" s="3">
         <v>460</v>
       </c>
     </row>
@@ -7602,7 +7603,7 @@
       <c r="D355" t="s">
         <v>345</v>
       </c>
-      <c r="E355" s="2">
+      <c r="E355" s="3">
         <v>-8.74</v>
       </c>
     </row>
@@ -7619,7 +7620,7 @@
       <c r="D356" t="s">
         <v>346</v>
       </c>
-      <c r="E356" s="2">
+      <c r="E356" s="3">
         <v>-0.44</v>
       </c>
     </row>
@@ -7636,7 +7637,7 @@
       <c r="D357" t="s">
         <v>343</v>
       </c>
-      <c r="E357" s="2">
+      <c r="E357" s="3">
         <v>-115315.88</v>
       </c>
     </row>
@@ -7653,7 +7654,7 @@
       <c r="D358" t="s">
         <v>347</v>
       </c>
-      <c r="E358" s="2">
+      <c r="E358" s="3">
         <v>1940</v>
       </c>
     </row>
@@ -7670,7 +7671,7 @@
       <c r="D359" t="s">
         <v>348</v>
       </c>
-      <c r="E359" s="2">
+      <c r="E359" s="3">
         <v>4710</v>
       </c>
     </row>
@@ -7687,7 +7688,7 @@
       <c r="D360" t="s">
         <v>349</v>
       </c>
-      <c r="E360" s="2">
+      <c r="E360" s="3">
         <v>15125</v>
       </c>
     </row>
@@ -7704,7 +7705,7 @@
       <c r="D361" t="s">
         <v>350</v>
       </c>
-      <c r="E361" s="2">
+      <c r="E361" s="3">
         <v>19237.5</v>
       </c>
     </row>
@@ -7721,7 +7722,7 @@
       <c r="D362" t="s">
         <v>351</v>
       </c>
-      <c r="E362" s="2">
+      <c r="E362" s="3">
         <v>2372.5</v>
       </c>
     </row>
@@ -7738,7 +7739,7 @@
       <c r="D363" t="s">
         <v>344</v>
       </c>
-      <c r="E363" s="2">
+      <c r="E363" s="3">
         <v>375</v>
       </c>
     </row>
@@ -7755,7 +7756,7 @@
       <c r="D364" t="s">
         <v>345</v>
       </c>
-      <c r="E364" s="2">
+      <c r="E364" s="3">
         <v>-7.13</v>
       </c>
     </row>
@@ -7772,7 +7773,7 @@
       <c r="D365" t="s">
         <v>346</v>
       </c>
-      <c r="E365" s="2">
+      <c r="E365" s="3">
         <v>-0.36</v>
       </c>
     </row>
@@ -7789,7 +7790,7 @@
       <c r="D366" t="s">
         <v>352</v>
       </c>
-      <c r="E366" s="2">
+      <c r="E366" s="3">
         <v>21961.82</v>
       </c>
     </row>
@@ -7806,7 +7807,7 @@
       <c r="D367" t="s">
         <v>343</v>
       </c>
-      <c r="E367" s="2">
+      <c r="E367" s="3">
         <v>-65714.33</v>
       </c>
     </row>
@@ -7823,7 +7824,7 @@
       <c r="D368" t="s">
         <v>353</v>
       </c>
-      <c r="E368" s="2">
+      <c r="E368" s="3">
         <v>54630.720000000001</v>
       </c>
     </row>
@@ -7840,7 +7841,7 @@
       <c r="D369" t="s">
         <v>343</v>
       </c>
-      <c r="E369" s="2">
+      <c r="E369" s="3">
         <v>-54630.720000000001</v>
       </c>
     </row>
@@ -7857,7 +7858,7 @@
       <c r="D370" t="s">
         <v>354</v>
       </c>
-      <c r="E370" s="2">
+      <c r="E370" s="3">
         <v>66895.23</v>
       </c>
     </row>
@@ -7874,7 +7875,7 @@
       <c r="D371" t="s">
         <v>343</v>
       </c>
-      <c r="E371" s="2">
+      <c r="E371" s="3">
         <v>-66895.23</v>
       </c>
     </row>
@@ -7891,7 +7892,7 @@
       <c r="D372" t="s">
         <v>344</v>
       </c>
-      <c r="E372" s="2">
+      <c r="E372" s="3">
         <v>685</v>
       </c>
     </row>
@@ -7908,7 +7909,7 @@
       <c r="D373" t="s">
         <v>345</v>
       </c>
-      <c r="E373" s="2">
+      <c r="E373" s="3">
         <v>-13.02</v>
       </c>
     </row>
@@ -7925,7 +7926,7 @@
       <c r="D374" t="s">
         <v>346</v>
       </c>
-      <c r="E374" s="2">
+      <c r="E374" s="3">
         <v>-0.66</v>
       </c>
     </row>
@@ -7942,7 +7943,7 @@
       <c r="D375" t="s">
         <v>355</v>
       </c>
-      <c r="E375" s="2">
+      <c r="E375" s="3">
         <v>630</v>
       </c>
     </row>
@@ -7959,7 +7960,7 @@
       <c r="D376" t="s">
         <v>356</v>
       </c>
-      <c r="E376" s="2">
+      <c r="E376" s="3">
         <v>-11.97</v>
       </c>
     </row>
@@ -7976,7 +7977,7 @@
       <c r="D377" t="s">
         <v>357</v>
       </c>
-      <c r="E377" s="2">
+      <c r="E377" s="3">
         <v>-0.6</v>
       </c>
     </row>
@@ -7993,7 +7994,7 @@
       <c r="D378" t="s">
         <v>347</v>
       </c>
-      <c r="E378" s="2">
+      <c r="E378" s="3">
         <v>825</v>
       </c>
     </row>
@@ -8010,7 +8011,7 @@
       <c r="D379" t="s">
         <v>348</v>
       </c>
-      <c r="E379" s="2">
+      <c r="E379" s="3">
         <v>4100</v>
       </c>
     </row>
@@ -8027,7 +8028,7 @@
       <c r="D380" t="s">
         <v>349</v>
       </c>
-      <c r="E380" s="2">
+      <c r="E380" s="3">
         <v>27160</v>
       </c>
     </row>
@@ -8044,7 +8045,7 @@
       <c r="D381" t="s">
         <v>350</v>
       </c>
-      <c r="E381" s="2">
+      <c r="E381" s="3">
         <v>23191.5</v>
       </c>
     </row>
@@ -8061,7 +8062,7 @@
       <c r="D382" t="s">
         <v>351</v>
       </c>
-      <c r="E382" s="2">
+      <c r="E382" s="3">
         <v>385</v>
       </c>
     </row>
@@ -8078,7 +8079,7 @@
       <c r="D383" t="s">
         <v>343</v>
       </c>
-      <c r="E383" s="2">
+      <c r="E383" s="3">
         <v>-56950.25</v>
       </c>
     </row>
@@ -8095,7 +8096,7 @@
       <c r="D384" t="s">
         <v>358</v>
       </c>
-      <c r="E384" s="2">
+      <c r="E384" s="3">
         <v>42792.83</v>
       </c>
     </row>
@@ -8112,7 +8113,7 @@
       <c r="D385" t="s">
         <v>344</v>
       </c>
-      <c r="E385" s="2">
+      <c r="E385" s="3">
         <v>360</v>
       </c>
     </row>
@@ -8129,7 +8130,7 @@
       <c r="D386" t="s">
         <v>345</v>
       </c>
-      <c r="E386" s="2">
+      <c r="E386" s="3">
         <v>-6.84</v>
       </c>
     </row>
@@ -8146,7 +8147,7 @@
       <c r="D387" t="s">
         <v>346</v>
       </c>
-      <c r="E387" s="2">
+      <c r="E387" s="3">
         <v>-0.34</v>
       </c>
     </row>
@@ -8163,7 +8164,7 @@
       <c r="D388" t="s">
         <v>344</v>
       </c>
-      <c r="E388" s="2">
+      <c r="E388" s="3">
         <v>650</v>
       </c>
     </row>
@@ -8180,7 +8181,7 @@
       <c r="D389" t="s">
         <v>345</v>
       </c>
-      <c r="E389" s="2">
+      <c r="E389" s="3">
         <v>-12.35</v>
       </c>
     </row>
@@ -8197,7 +8198,7 @@
       <c r="D390" t="s">
         <v>346</v>
       </c>
-      <c r="E390" s="2">
+      <c r="E390" s="3">
         <v>-0.62</v>
       </c>
     </row>
@@ -8214,7 +8215,7 @@
       <c r="D391" t="s">
         <v>347</v>
       </c>
-      <c r="E391" s="2">
+      <c r="E391" s="3">
         <v>1295</v>
       </c>
     </row>
@@ -8231,7 +8232,7 @@
       <c r="D392" t="s">
         <v>348</v>
       </c>
-      <c r="E392" s="2">
+      <c r="E392" s="3">
         <v>3540</v>
       </c>
     </row>
@@ -8248,7 +8249,7 @@
       <c r="D393" t="s">
         <v>349</v>
       </c>
-      <c r="E393" s="2">
+      <c r="E393" s="3">
         <v>25725</v>
       </c>
     </row>
@@ -8265,7 +8266,7 @@
       <c r="D394" t="s">
         <v>350</v>
       </c>
-      <c r="E394" s="2">
+      <c r="E394" s="3">
         <v>20000</v>
       </c>
     </row>
@@ -8282,7 +8283,7 @@
       <c r="D395" t="s">
         <v>351</v>
       </c>
-      <c r="E395" s="2">
+      <c r="E395" s="3">
         <v>1014</v>
       </c>
     </row>
@@ -8299,7 +8300,7 @@
       <c r="D396" t="s">
         <v>348</v>
       </c>
-      <c r="E396" s="2">
+      <c r="E396" s="3">
         <v>1450</v>
       </c>
     </row>
@@ -8316,7 +8317,7 @@
       <c r="D397" t="s">
         <v>349</v>
       </c>
-      <c r="E397" s="2">
+      <c r="E397" s="3">
         <v>10355</v>
       </c>
     </row>
@@ -8333,7 +8334,7 @@
       <c r="D398" t="s">
         <v>350</v>
       </c>
-      <c r="E398" s="2">
+      <c r="E398" s="3">
         <v>9800</v>
       </c>
     </row>
@@ -8350,7 +8351,7 @@
       <c r="D399" t="s">
         <v>351</v>
       </c>
-      <c r="E399" s="2">
+      <c r="E399" s="3">
         <v>650</v>
       </c>
     </row>
@@ -8367,7 +8368,7 @@
       <c r="D400" t="s">
         <v>359</v>
       </c>
-      <c r="E400" s="2">
+      <c r="E400" s="3">
         <v>24886.95</v>
       </c>
     </row>
@@ -8384,7 +8385,7 @@
       <c r="D401" t="s">
         <v>348</v>
       </c>
-      <c r="E401" s="2">
+      <c r="E401" s="3">
         <v>5030</v>
       </c>
     </row>
@@ -8401,7 +8402,7 @@
       <c r="D402" t="s">
         <v>349</v>
       </c>
-      <c r="E402" s="2">
+      <c r="E402" s="3">
         <v>14445</v>
       </c>
     </row>
@@ -8418,7 +8419,7 @@
       <c r="D403" t="s">
         <v>350</v>
       </c>
-      <c r="E403" s="2">
+      <c r="E403" s="3">
         <v>5035</v>
       </c>
     </row>
@@ -8435,7 +8436,7 @@
       <c r="D404" t="s">
         <v>351</v>
       </c>
-      <c r="E404" s="2">
+      <c r="E404" s="3">
         <v>1800</v>
       </c>
     </row>
@@ -8452,7 +8453,7 @@
       <c r="D405" t="s">
         <v>344</v>
       </c>
-      <c r="E405" s="2">
+      <c r="E405" s="3">
         <v>725</v>
       </c>
     </row>
@@ -8469,7 +8470,7 @@
       <c r="D406" t="s">
         <v>345</v>
       </c>
-      <c r="E406" s="2">
+      <c r="E406" s="3">
         <v>-13.78</v>
       </c>
     </row>
@@ -8486,7 +8487,7 @@
       <c r="D407" t="s">
         <v>346</v>
       </c>
-      <c r="E407" s="2">
+      <c r="E407" s="3">
         <v>-0.69</v>
       </c>
     </row>
@@ -8503,7 +8504,7 @@
       <c r="D408" t="s">
         <v>343</v>
       </c>
-      <c r="E408" s="2">
+      <c r="E408" s="3">
         <v>-169519.16</v>
       </c>
     </row>
@@ -8520,7 +8521,7 @@
       <c r="D409" t="s">
         <v>348</v>
       </c>
-      <c r="E409" s="2">
+      <c r="E409" s="3">
         <v>1840</v>
       </c>
     </row>
@@ -8537,7 +8538,7 @@
       <c r="D410" t="s">
         <v>349</v>
       </c>
-      <c r="E410" s="2">
+      <c r="E410" s="3">
         <v>15800</v>
       </c>
     </row>
@@ -8554,7 +8555,7 @@
       <c r="D411" t="s">
         <v>350</v>
       </c>
-      <c r="E411" s="2">
+      <c r="E411" s="3">
         <v>15462.5</v>
       </c>
     </row>
@@ -8571,7 +8572,7 @@
       <c r="D412" t="s">
         <v>351</v>
       </c>
-      <c r="E412" s="2">
+      <c r="E412" s="3">
         <v>465</v>
       </c>
     </row>
@@ -8588,7 +8589,7 @@
       <c r="D413" t="s">
         <v>343</v>
       </c>
-      <c r="E413" s="2">
+      <c r="E413" s="3">
         <v>-33567.5</v>
       </c>
     </row>
@@ -8605,7 +8606,7 @@
       <c r="D414" t="s">
         <v>348</v>
       </c>
-      <c r="E414" s="2">
+      <c r="E414" s="3">
         <v>2035</v>
       </c>
     </row>
@@ -8622,7 +8623,7 @@
       <c r="D415" t="s">
         <v>349</v>
       </c>
-      <c r="E415" s="2">
+      <c r="E415" s="3">
         <v>13983</v>
       </c>
     </row>
@@ -8639,7 +8640,7 @@
       <c r="D416" t="s">
         <v>350</v>
       </c>
-      <c r="E416" s="2">
+      <c r="E416" s="3">
         <v>12993</v>
       </c>
     </row>
@@ -8656,7 +8657,7 @@
       <c r="D417" t="s">
         <v>351</v>
       </c>
-      <c r="E417" s="2">
+      <c r="E417" s="3">
         <v>2665</v>
       </c>
     </row>
@@ -8673,7 +8674,7 @@
       <c r="D418" t="s">
         <v>344</v>
       </c>
-      <c r="E418" s="2">
+      <c r="E418" s="3">
         <v>1685</v>
       </c>
     </row>
@@ -8690,7 +8691,7 @@
       <c r="D419" t="s">
         <v>345</v>
       </c>
-      <c r="E419" s="2">
+      <c r="E419" s="3">
         <v>-32.020000000000003</v>
       </c>
     </row>
@@ -8707,7 +8708,7 @@
       <c r="D420" t="s">
         <v>346</v>
       </c>
-      <c r="E420" s="2">
+      <c r="E420" s="3">
         <v>-1.6</v>
       </c>
     </row>
@@ -8724,7 +8725,7 @@
       <c r="D421" t="s">
         <v>348</v>
       </c>
-      <c r="E421" s="2">
+      <c r="E421" s="3">
         <v>1715</v>
       </c>
     </row>
@@ -8741,7 +8742,7 @@
       <c r="D422" t="s">
         <v>349</v>
       </c>
-      <c r="E422" s="2">
+      <c r="E422" s="3">
         <v>17560</v>
       </c>
     </row>
@@ -8758,7 +8759,7 @@
       <c r="D423" t="s">
         <v>350</v>
       </c>
-      <c r="E423" s="2">
+      <c r="E423" s="3">
         <v>16002.5</v>
       </c>
     </row>
@@ -8775,7 +8776,7 @@
       <c r="D424" t="s">
         <v>351</v>
       </c>
-      <c r="E424" s="2">
+      <c r="E424" s="3">
         <v>1090</v>
       </c>
     </row>
@@ -8792,7 +8793,7 @@
       <c r="D425" t="s">
         <v>343</v>
       </c>
-      <c r="E425" s="2">
+      <c r="E425" s="3">
         <v>-69694.880000000005</v>
       </c>
     </row>
@@ -8809,7 +8810,7 @@
       <c r="D426" t="s">
         <v>347</v>
       </c>
-      <c r="E426" s="2">
+      <c r="E426" s="3">
         <v>335</v>
       </c>
     </row>
@@ -8826,7 +8827,7 @@
       <c r="D427" t="s">
         <v>348</v>
       </c>
-      <c r="E427" s="2">
+      <c r="E427" s="3">
         <v>2110</v>
       </c>
     </row>
@@ -8843,7 +8844,7 @@
       <c r="D428" t="s">
         <v>349</v>
       </c>
-      <c r="E428" s="2">
+      <c r="E428" s="3">
         <v>19522.5</v>
       </c>
     </row>
@@ -8860,7 +8861,7 @@
       <c r="D429" t="s">
         <v>350</v>
       </c>
-      <c r="E429" s="2">
+      <c r="E429" s="3">
         <v>17407.5</v>
       </c>
     </row>
@@ -8877,7 +8878,7 @@
       <c r="D430" t="s">
         <v>351</v>
       </c>
-      <c r="E430" s="2">
+      <c r="E430" s="3">
         <v>395</v>
       </c>
     </row>
@@ -8894,7 +8895,7 @@
       <c r="D431" t="s">
         <v>343</v>
       </c>
-      <c r="E431" s="2">
+      <c r="E431" s="3">
         <v>-39770</v>
       </c>
     </row>
@@ -8911,7 +8912,7 @@
       <c r="D432" t="s">
         <v>349</v>
       </c>
-      <c r="E432" s="2">
+      <c r="E432" s="3">
         <v>18130</v>
       </c>
     </row>
@@ -8928,7 +8929,7 @@
       <c r="D433" t="s">
         <v>350</v>
       </c>
-      <c r="E433" s="2">
+      <c r="E433" s="3">
         <v>13840</v>
       </c>
     </row>
@@ -8945,7 +8946,7 @@
       <c r="D434" t="s">
         <v>351</v>
       </c>
-      <c r="E434" s="2">
+      <c r="E434" s="3">
         <v>1385</v>
       </c>
     </row>
@@ -8962,7 +8963,7 @@
       <c r="D435" t="s">
         <v>347</v>
       </c>
-      <c r="E435" s="2">
+      <c r="E435" s="3">
         <v>1110</v>
       </c>
     </row>
@@ -8979,7 +8980,7 @@
       <c r="D436" t="s">
         <v>348</v>
       </c>
-      <c r="E436" s="2">
+      <c r="E436" s="3">
         <v>1790</v>
       </c>
     </row>
@@ -8996,7 +8997,7 @@
       <c r="D437" t="s">
         <v>344</v>
       </c>
-      <c r="E437" s="2">
+      <c r="E437" s="3">
         <v>415</v>
       </c>
     </row>
@@ -9013,7 +9014,7 @@
       <c r="D438" t="s">
         <v>345</v>
       </c>
-      <c r="E438" s="2">
+      <c r="E438" s="3">
         <v>-7.89</v>
       </c>
     </row>
@@ -9030,7 +9031,7 @@
       <c r="D439" t="s">
         <v>346</v>
       </c>
-      <c r="E439" s="2">
+      <c r="E439" s="3">
         <v>-0.39</v>
       </c>
     </row>
@@ -9047,7 +9048,7 @@
       <c r="D440" t="s">
         <v>343</v>
       </c>
-      <c r="E440" s="2">
+      <c r="E440" s="3">
         <v>-36661.72</v>
       </c>
     </row>
@@ -9064,7 +9065,7 @@
       <c r="D441" t="s">
         <v>347</v>
       </c>
-      <c r="E441" s="2">
+      <c r="E441" s="3">
         <v>290</v>
       </c>
     </row>
@@ -9081,7 +9082,7 @@
       <c r="D442" t="s">
         <v>348</v>
       </c>
-      <c r="E442" s="2">
+      <c r="E442" s="3">
         <v>535</v>
       </c>
     </row>
@@ -9098,7 +9099,7 @@
       <c r="D443" t="s">
         <v>349</v>
       </c>
-      <c r="E443" s="2">
+      <c r="E443" s="3">
         <v>19365</v>
       </c>
     </row>
@@ -9115,7 +9116,7 @@
       <c r="D444" t="s">
         <v>350</v>
       </c>
-      <c r="E444" s="2">
+      <c r="E444" s="3">
         <v>9625</v>
       </c>
     </row>
@@ -9132,7 +9133,7 @@
       <c r="D445" t="s">
         <v>351</v>
       </c>
-      <c r="E445" s="2">
+      <c r="E445" s="3">
         <v>1115</v>
       </c>
     </row>
@@ -9149,7 +9150,7 @@
       <c r="D446" t="s">
         <v>344</v>
       </c>
-      <c r="E446" s="2">
+      <c r="E446" s="3">
         <v>580</v>
       </c>
     </row>
@@ -9166,7 +9167,7 @@
       <c r="D447" t="s">
         <v>345</v>
       </c>
-      <c r="E447" s="2">
+      <c r="E447" s="3">
         <v>-11.02</v>
       </c>
     </row>
@@ -9183,7 +9184,7 @@
       <c r="D448" t="s">
         <v>346</v>
       </c>
-      <c r="E448" s="2">
+      <c r="E448" s="3">
         <v>-0.55000000000000004</v>
       </c>
     </row>
@@ -9200,7 +9201,7 @@
       <c r="D449" t="s">
         <v>361</v>
       </c>
-      <c r="E449" s="2">
+      <c r="E449" s="3">
         <v>29272.3</v>
       </c>
     </row>
@@ -9217,7 +9218,7 @@
       <c r="D450" t="s">
         <v>343</v>
       </c>
-      <c r="E450" s="2">
+      <c r="E450" s="3">
         <v>-60770.73</v>
       </c>
     </row>
@@ -9234,7 +9235,7 @@
       <c r="D451" t="s">
         <v>362</v>
       </c>
-      <c r="E451" s="2">
+      <c r="E451" s="3">
         <v>-600</v>
       </c>
     </row>
@@ -9251,7 +9252,7 @@
       <c r="D452" t="s">
         <v>348</v>
       </c>
-      <c r="E452" s="2">
+      <c r="E452" s="3">
         <v>3550</v>
       </c>
     </row>
@@ -9268,7 +9269,7 @@
       <c r="D453" t="s">
         <v>349</v>
       </c>
-      <c r="E453" s="2">
+      <c r="E453" s="3">
         <v>36538</v>
       </c>
     </row>
@@ -9285,7 +9286,7 @@
       <c r="D454" t="s">
         <v>350</v>
       </c>
-      <c r="E454" s="2">
+      <c r="E454" s="3">
         <v>23152</v>
       </c>
     </row>
@@ -9302,7 +9303,7 @@
       <c r="D455" t="s">
         <v>351</v>
       </c>
-      <c r="E455" s="2">
+      <c r="E455" s="3">
         <v>2125</v>
       </c>
     </row>
@@ -9319,7 +9320,7 @@
       <c r="D456" t="s">
         <v>363</v>
       </c>
-      <c r="E456" s="2">
+      <c r="E456" s="3">
         <v>-64765</v>
       </c>
     </row>
@@ -9336,7 +9337,7 @@
       <c r="D457" t="s">
         <v>348</v>
       </c>
-      <c r="E457" s="2">
+      <c r="E457" s="3">
         <v>5310</v>
       </c>
     </row>
@@ -9353,7 +9354,7 @@
       <c r="D458" t="s">
         <v>349</v>
       </c>
-      <c r="E458" s="2">
+      <c r="E458" s="3">
         <v>30817</v>
       </c>
     </row>
@@ -9370,7 +9371,7 @@
       <c r="D459" t="s">
         <v>364</v>
       </c>
-      <c r="E459" s="2">
+      <c r="E459" s="3">
         <v>820</v>
       </c>
     </row>
@@ -9387,7 +9388,7 @@
       <c r="D460" t="s">
         <v>350</v>
       </c>
-      <c r="E460" s="2">
+      <c r="E460" s="3">
         <v>20688</v>
       </c>
     </row>
@@ -9404,7 +9405,7 @@
       <c r="D461" t="s">
         <v>351</v>
       </c>
-      <c r="E461" s="2">
+      <c r="E461" s="3">
         <v>1710</v>
       </c>
     </row>
@@ -9421,7 +9422,7 @@
       <c r="D462" t="s">
         <v>344</v>
       </c>
-      <c r="E462" s="2">
+      <c r="E462" s="3">
         <v>1035</v>
       </c>
     </row>
@@ -9438,7 +9439,7 @@
       <c r="D463" t="s">
         <v>345</v>
       </c>
-      <c r="E463" s="2">
+      <c r="E463" s="3">
         <v>-19.670000000000002</v>
       </c>
     </row>
@@ -9455,7 +9456,7 @@
       <c r="D464" t="s">
         <v>346</v>
       </c>
-      <c r="E464" s="2">
+      <c r="E464" s="3">
         <v>-0.98</v>
       </c>
     </row>
@@ -9472,7 +9473,7 @@
       <c r="D465" t="s">
         <v>343</v>
       </c>
-      <c r="E465" s="2">
+      <c r="E465" s="3">
         <v>-60359.35</v>
       </c>
     </row>
@@ -9489,7 +9490,7 @@
       <c r="D466" t="s">
         <v>348</v>
       </c>
-      <c r="E466" s="2">
+      <c r="E466" s="3">
         <v>4130</v>
       </c>
     </row>
@@ -9506,7 +9507,7 @@
       <c r="D467" t="s">
         <v>349</v>
       </c>
-      <c r="E467" s="2">
+      <c r="E467" s="3">
         <v>17470</v>
       </c>
     </row>
@@ -9523,7 +9524,7 @@
       <c r="D468" t="s">
         <v>350</v>
       </c>
-      <c r="E468" s="2">
+      <c r="E468" s="3">
         <v>14405</v>
       </c>
     </row>
@@ -9540,7 +9541,7 @@
       <c r="D469" t="s">
         <v>351</v>
       </c>
-      <c r="E469" s="2">
+      <c r="E469" s="3">
         <v>2835</v>
       </c>
     </row>
@@ -9557,7 +9558,7 @@
       <c r="D470" t="s">
         <v>343</v>
       </c>
-      <c r="E470" s="2">
+      <c r="E470" s="3">
         <v>-38840</v>
       </c>
     </row>
@@ -9574,7 +9575,7 @@
       <c r="D471" t="s">
         <v>347</v>
       </c>
-      <c r="E471" s="2">
+      <c r="E471" s="3">
         <v>790</v>
       </c>
     </row>
@@ -9591,7 +9592,7 @@
       <c r="D472" t="s">
         <v>348</v>
       </c>
-      <c r="E472" s="2">
+      <c r="E472" s="3">
         <v>4030</v>
       </c>
     </row>
@@ -9608,7 +9609,7 @@
       <c r="D473" t="s">
         <v>349</v>
       </c>
-      <c r="E473" s="2">
+      <c r="E473" s="3">
         <v>24280</v>
       </c>
     </row>
@@ -9625,7 +9626,7 @@
       <c r="D474" t="s">
         <v>350</v>
       </c>
-      <c r="E474" s="2">
+      <c r="E474" s="3">
         <v>13400</v>
       </c>
     </row>
@@ -9642,7 +9643,7 @@
       <c r="D475" t="s">
         <v>343</v>
       </c>
-      <c r="E475" s="2">
+      <c r="E475" s="3">
         <v>-42500</v>
       </c>
     </row>
@@ -9659,7 +9660,7 @@
       <c r="D476" t="s">
         <v>365</v>
       </c>
-      <c r="E476" s="2">
+      <c r="E476" s="3">
         <v>36979.96</v>
       </c>
     </row>
@@ -9676,7 +9677,7 @@
       <c r="D477" t="s">
         <v>366</v>
       </c>
-      <c r="E477" s="2">
+      <c r="E477" s="3">
         <v>54469.98</v>
       </c>
     </row>
@@ -9693,7 +9694,7 @@
       <c r="D478" t="s">
         <v>343</v>
       </c>
-      <c r="E478" s="2">
+      <c r="E478" s="3">
         <v>-91449.94</v>
       </c>
     </row>
@@ -9710,7 +9711,7 @@
       <c r="D479" t="s">
         <v>344</v>
       </c>
-      <c r="E479" s="2">
+      <c r="E479" s="3">
         <v>750</v>
       </c>
     </row>
@@ -9727,7 +9728,7 @@
       <c r="D480" t="s">
         <v>345</v>
       </c>
-      <c r="E480" s="2">
+      <c r="E480" s="3">
         <v>-14.25</v>
       </c>
     </row>
@@ -9744,7 +9745,7 @@
       <c r="D481" t="s">
         <v>346</v>
       </c>
-      <c r="E481" s="2">
+      <c r="E481" s="3">
         <v>-0.71</v>
       </c>
     </row>
@@ -9761,7 +9762,7 @@
       <c r="D482" t="s">
         <v>348</v>
       </c>
-      <c r="E482" s="2">
+      <c r="E482" s="3">
         <v>1888.5</v>
       </c>
     </row>
@@ -9778,7 +9779,7 @@
       <c r="D483" t="s">
         <v>349</v>
       </c>
-      <c r="E483" s="2">
+      <c r="E483" s="3">
         <v>21430</v>
       </c>
     </row>
@@ -9795,7 +9796,7 @@
       <c r="D484" t="s">
         <v>350</v>
       </c>
-      <c r="E484" s="2">
+      <c r="E484" s="3">
         <v>19311</v>
       </c>
     </row>
@@ -9812,7 +9813,7 @@
       <c r="D485" t="s">
         <v>351</v>
       </c>
-      <c r="E485" s="2">
+      <c r="E485" s="3">
         <v>740</v>
       </c>
     </row>
@@ -9829,7 +9830,7 @@
       <c r="D486" t="s">
         <v>347</v>
       </c>
-      <c r="E486" s="2">
+      <c r="E486" s="3">
         <v>1565</v>
       </c>
     </row>
@@ -9846,7 +9847,7 @@
       <c r="D487" t="s">
         <v>348</v>
       </c>
-      <c r="E487" s="2">
+      <c r="E487" s="3">
         <v>2455</v>
       </c>
     </row>
@@ -9863,7 +9864,7 @@
       <c r="D488" t="s">
         <v>349</v>
       </c>
-      <c r="E488" s="2">
+      <c r="E488" s="3">
         <v>24810</v>
       </c>
     </row>
@@ -9880,7 +9881,7 @@
       <c r="D489" t="s">
         <v>350</v>
       </c>
-      <c r="E489" s="2">
+      <c r="E489" s="3">
         <v>8990</v>
       </c>
     </row>
@@ -9897,7 +9898,7 @@
       <c r="D490" t="s">
         <v>351</v>
       </c>
-      <c r="E490" s="2">
+      <c r="E490" s="3">
         <v>1850</v>
       </c>
     </row>
@@ -9914,7 +9915,7 @@
       <c r="D491" t="s">
         <v>343</v>
       </c>
-      <c r="E491" s="2">
+      <c r="E491" s="3">
         <v>-83774.539999999994</v>
       </c>
     </row>
@@ -9931,7 +9932,7 @@
       <c r="D492" t="s">
         <v>367</v>
       </c>
-      <c r="E492" s="2">
+      <c r="E492" s="3">
         <v>81271.81</v>
       </c>
     </row>
@@ -9948,7 +9949,7 @@
       <c r="D493" t="s">
         <v>368</v>
       </c>
-      <c r="E493" s="2">
+      <c r="E493" s="3">
         <v>76409.37</v>
       </c>
     </row>
@@ -9965,7 +9966,7 @@
       <c r="D494" t="s">
         <v>347</v>
       </c>
-      <c r="E494" s="2">
+      <c r="E494" s="3">
         <v>1175</v>
       </c>
     </row>
@@ -9982,7 +9983,7 @@
       <c r="D495" t="s">
         <v>348</v>
       </c>
-      <c r="E495" s="2">
+      <c r="E495" s="3">
         <v>2176</v>
       </c>
     </row>
@@ -9999,7 +10000,7 @@
       <c r="D496" t="s">
         <v>349</v>
       </c>
-      <c r="E496" s="2">
+      <c r="E496" s="3">
         <v>34555</v>
       </c>
     </row>
@@ -10016,7 +10017,7 @@
       <c r="D497" t="s">
         <v>351</v>
       </c>
-      <c r="E497" s="2">
+      <c r="E497" s="3">
         <v>2580</v>
       </c>
     </row>
@@ -10033,7 +10034,7 @@
       <c r="D498" t="s">
         <v>350</v>
       </c>
-      <c r="E498" s="2">
+      <c r="E498" s="3">
         <v>25330</v>
       </c>
     </row>
@@ -10050,7 +10051,7 @@
       <c r="D499" t="s">
         <v>355</v>
       </c>
-      <c r="E499" s="2">
+      <c r="E499" s="3">
         <v>1725</v>
       </c>
     </row>
@@ -10067,7 +10068,7 @@
       <c r="D500" t="s">
         <v>356</v>
       </c>
-      <c r="E500" s="2">
+      <c r="E500" s="3">
         <v>-32.78</v>
       </c>
     </row>
@@ -10084,7 +10085,7 @@
       <c r="D501" t="s">
         <v>357</v>
       </c>
-      <c r="E501" s="2">
+      <c r="E501" s="3">
         <v>-1.64</v>
       </c>
     </row>
@@ -10101,7 +10102,7 @@
       <c r="D502" t="s">
         <v>347</v>
       </c>
-      <c r="E502" s="2">
+      <c r="E502" s="3">
         <v>690</v>
       </c>
     </row>
@@ -10118,7 +10119,7 @@
       <c r="D503" t="s">
         <v>348</v>
       </c>
-      <c r="E503" s="2">
+      <c r="E503" s="3">
         <v>2650</v>
       </c>
     </row>
@@ -10135,7 +10136,7 @@
       <c r="D504" t="s">
         <v>349</v>
       </c>
-      <c r="E504" s="2">
+      <c r="E504" s="3">
         <v>38938</v>
       </c>
     </row>
@@ -10152,7 +10153,7 @@
       <c r="D505" t="s">
         <v>350</v>
       </c>
-      <c r="E505" s="2">
+      <c r="E505" s="3">
         <v>13972</v>
       </c>
     </row>
@@ -10169,7 +10170,7 @@
       <c r="D506" t="s">
         <v>351</v>
       </c>
-      <c r="E506" s="2">
+      <c r="E506" s="3">
         <v>3450</v>
       </c>
     </row>
@@ -10186,7 +10187,7 @@
       <c r="D507" t="s">
         <v>348</v>
       </c>
-      <c r="E507" s="2">
+      <c r="E507" s="3">
         <v>3070</v>
       </c>
     </row>
@@ -10203,7 +10204,7 @@
       <c r="D508" t="s">
         <v>349</v>
       </c>
-      <c r="E508" s="2">
+      <c r="E508" s="3">
         <v>28615</v>
       </c>
     </row>
@@ -10220,7 +10221,7 @@
       <c r="D509" t="s">
         <v>350</v>
       </c>
-      <c r="E509" s="2">
+      <c r="E509" s="3">
         <v>20055</v>
       </c>
     </row>
@@ -10237,7 +10238,7 @@
       <c r="D510" t="s">
         <v>351</v>
       </c>
-      <c r="E510" s="2">
+      <c r="E510" s="3">
         <v>4485</v>
       </c>
     </row>
@@ -10254,7 +10255,7 @@
       <c r="D511" t="s">
         <v>344</v>
       </c>
-      <c r="E511" s="2">
+      <c r="E511" s="3">
         <v>640</v>
       </c>
     </row>
@@ -10271,7 +10272,7 @@
       <c r="D512" t="s">
         <v>345</v>
       </c>
-      <c r="E512" s="2">
+      <c r="E512" s="3">
         <v>-12.16</v>
       </c>
     </row>
@@ -10288,7 +10289,7 @@
       <c r="D513" t="s">
         <v>346</v>
       </c>
-      <c r="E513" s="2">
+      <c r="E513" s="3">
         <v>-0.61</v>
       </c>
     </row>
@@ -10305,7 +10306,7 @@
       <c r="D514" t="s">
         <v>355</v>
       </c>
-      <c r="E514" s="2">
+      <c r="E514" s="3">
         <v>1300</v>
       </c>
     </row>
@@ -10322,7 +10323,7 @@
       <c r="D515" t="s">
         <v>356</v>
       </c>
-      <c r="E515" s="2">
+      <c r="E515" s="3">
         <v>-24.7</v>
       </c>
     </row>
@@ -10339,7 +10340,7 @@
       <c r="D516" t="s">
         <v>357</v>
       </c>
-      <c r="E516" s="2">
+      <c r="E516" s="3">
         <v>-1.24</v>
       </c>
     </row>
@@ -10356,7 +10357,7 @@
       <c r="D517" t="s">
         <v>343</v>
       </c>
-      <c r="E517" s="2">
+      <c r="E517" s="3">
         <v>-120000</v>
       </c>
     </row>
@@ -10373,7 +10374,7 @@
       <c r="D518" t="s">
         <v>347</v>
       </c>
-      <c r="E518" s="2">
+      <c r="E518" s="3">
         <v>370</v>
       </c>
     </row>
@@ -10390,7 +10391,7 @@
       <c r="D519" t="s">
         <v>348</v>
       </c>
-      <c r="E519" s="2">
+      <c r="E519" s="3">
         <v>1215</v>
       </c>
     </row>
@@ -10407,7 +10408,7 @@
       <c r="D520" t="s">
         <v>349</v>
       </c>
-      <c r="E520" s="2">
+      <c r="E520" s="3">
         <v>15590</v>
       </c>
     </row>
@@ -10424,7 +10425,7 @@
       <c r="D521" t="s">
         <v>350</v>
       </c>
-      <c r="E521" s="2">
+      <c r="E521" s="3">
         <v>10070</v>
       </c>
     </row>
@@ -10441,7 +10442,7 @@
       <c r="D522" t="s">
         <v>351</v>
       </c>
-      <c r="E522" s="2">
+      <c r="E522" s="3">
         <v>290</v>
       </c>
     </row>
@@ -10458,7 +10459,7 @@
       <c r="D523" t="s">
         <v>348</v>
       </c>
-      <c r="E523" s="2">
+      <c r="E523" s="3">
         <v>2480</v>
       </c>
     </row>
@@ -10475,7 +10476,7 @@
       <c r="D524" t="s">
         <v>349</v>
       </c>
-      <c r="E524" s="2">
+      <c r="E524" s="3">
         <v>23380</v>
       </c>
     </row>
@@ -10492,7 +10493,7 @@
       <c r="D525" t="s">
         <v>350</v>
       </c>
-      <c r="E525" s="2">
+      <c r="E525" s="3">
         <v>20235</v>
       </c>
     </row>
@@ -10509,7 +10510,7 @@
       <c r="D526" t="s">
         <v>351</v>
       </c>
-      <c r="E526" s="2">
+      <c r="E526" s="3">
         <v>2790</v>
       </c>
     </row>
@@ -10526,7 +10527,7 @@
       <c r="D527" t="s">
         <v>343</v>
       </c>
-      <c r="E527" s="2">
+      <c r="E527" s="3">
         <v>-299434.05</v>
       </c>
     </row>
@@ -10543,7 +10544,7 @@
       <c r="D528" t="s">
         <v>348</v>
       </c>
-      <c r="E528" s="2">
+      <c r="E528" s="3">
         <v>2585</v>
       </c>
     </row>
@@ -10560,7 +10561,7 @@
       <c r="D529" t="s">
         <v>349</v>
       </c>
-      <c r="E529" s="2">
+      <c r="E529" s="3">
         <v>28485</v>
       </c>
     </row>
@@ -10577,7 +10578,7 @@
       <c r="D530" t="s">
         <v>350</v>
       </c>
-      <c r="E530" s="2">
+      <c r="E530" s="3">
         <v>15015</v>
       </c>
     </row>
@@ -10594,7 +10595,7 @@
       <c r="D531" t="s">
         <v>351</v>
       </c>
-      <c r="E531" s="2">
+      <c r="E531" s="3">
         <v>1450</v>
       </c>
     </row>
@@ -10611,7 +10612,7 @@
       <c r="D532" t="s">
         <v>343</v>
       </c>
-      <c r="E532" s="2">
+      <c r="E532" s="3">
         <v>-47535</v>
       </c>
     </row>
@@ -10628,7 +10629,7 @@
       <c r="D533" t="s">
         <v>348</v>
       </c>
-      <c r="E533" s="2">
+      <c r="E533" s="3">
         <v>4675</v>
       </c>
     </row>
@@ -10645,7 +10646,7 @@
       <c r="D534" t="s">
         <v>349</v>
       </c>
-      <c r="E534" s="2">
+      <c r="E534" s="3">
         <v>26025</v>
       </c>
     </row>
@@ -10662,7 +10663,7 @@
       <c r="D535" t="s">
         <v>350</v>
       </c>
-      <c r="E535" s="2">
+      <c r="E535" s="3">
         <v>16850</v>
       </c>
     </row>
@@ -10679,7 +10680,7 @@
       <c r="D536" t="s">
         <v>348</v>
       </c>
-      <c r="E536" s="2">
+      <c r="E536" s="3">
         <v>3275</v>
       </c>
     </row>
@@ -10696,7 +10697,7 @@
       <c r="D537" t="s">
         <v>349</v>
       </c>
-      <c r="E537" s="2">
+      <c r="E537" s="3">
         <v>21480</v>
       </c>
     </row>
@@ -10713,7 +10714,7 @@
       <c r="D538" t="s">
         <v>364</v>
       </c>
-      <c r="E538" s="2">
+      <c r="E538" s="3">
         <v>710</v>
       </c>
     </row>
@@ -10730,7 +10731,7 @@
       <c r="D539" t="s">
         <v>350</v>
       </c>
-      <c r="E539" s="2">
+      <c r="E539" s="3">
         <v>12985</v>
       </c>
     </row>
@@ -10747,7 +10748,7 @@
       <c r="D540" t="s">
         <v>351</v>
       </c>
-      <c r="E540" s="2">
+      <c r="E540" s="3">
         <v>1305</v>
       </c>
     </row>
@@ -10764,7 +10765,7 @@
       <c r="D541" t="s">
         <v>355</v>
       </c>
-      <c r="E541" s="2">
+      <c r="E541" s="3">
         <v>360</v>
       </c>
     </row>
@@ -10781,7 +10782,7 @@
       <c r="D542" t="s">
         <v>356</v>
       </c>
-      <c r="E542" s="2">
+      <c r="E542" s="3">
         <v>-6.84</v>
       </c>
     </row>
@@ -10798,7 +10799,7 @@
       <c r="D543" t="s">
         <v>357</v>
       </c>
-      <c r="E543" s="2">
+      <c r="E543" s="3">
         <v>-0.34</v>
       </c>
     </row>
@@ -10815,7 +10816,7 @@
       <c r="D544" t="s">
         <v>347</v>
       </c>
-      <c r="E544" s="2">
+      <c r="E544" s="3">
         <v>290</v>
       </c>
     </row>
@@ -10832,7 +10833,7 @@
       <c r="D545" t="s">
         <v>348</v>
       </c>
-      <c r="E545" s="2">
+      <c r="E545" s="3">
         <v>8740</v>
       </c>
     </row>
@@ -10849,7 +10850,7 @@
       <c r="D546" t="s">
         <v>349</v>
       </c>
-      <c r="E546" s="2">
+      <c r="E546" s="3">
         <v>18605</v>
       </c>
     </row>
@@ -10866,7 +10867,7 @@
       <c r="D547" t="s">
         <v>350</v>
       </c>
-      <c r="E547" s="2">
+      <c r="E547" s="3">
         <v>7510</v>
       </c>
     </row>
@@ -10883,7 +10884,7 @@
       <c r="D548" t="s">
         <v>351</v>
       </c>
-      <c r="E548" s="2">
+      <c r="E548" s="3">
         <v>1440</v>
       </c>
     </row>
@@ -10900,7 +10901,7 @@
       <c r="D549" t="s">
         <v>369</v>
       </c>
-      <c r="E549" s="2">
+      <c r="E549" s="3">
         <v>30583</v>
       </c>
     </row>
@@ -10917,7 +10918,7 @@
       <c r="D550" t="s">
         <v>343</v>
       </c>
-      <c r="E550" s="2">
+      <c r="E550" s="3">
         <v>-154825.82</v>
       </c>
     </row>
@@ -10934,7 +10935,7 @@
       <c r="D551" t="s">
         <v>347</v>
       </c>
-      <c r="E551" s="2">
+      <c r="E551" s="3">
         <v>1260</v>
       </c>
     </row>
@@ -10951,7 +10952,7 @@
       <c r="D552" t="s">
         <v>348</v>
       </c>
-      <c r="E552" s="2">
+      <c r="E552" s="3">
         <v>2850</v>
       </c>
     </row>
@@ -10968,7 +10969,7 @@
       <c r="D553" t="s">
         <v>349</v>
       </c>
-      <c r="E553" s="2">
+      <c r="E553" s="3">
         <v>23395</v>
       </c>
     </row>
@@ -10985,7 +10986,7 @@
       <c r="D554" t="s">
         <v>350</v>
       </c>
-      <c r="E554" s="2">
+      <c r="E554" s="3">
         <v>16256</v>
       </c>
     </row>
@@ -11002,7 +11003,7 @@
       <c r="D555" t="s">
         <v>351</v>
       </c>
-      <c r="E555" s="2">
+      <c r="E555" s="3">
         <v>2355</v>
       </c>
     </row>
@@ -11019,7 +11020,7 @@
       <c r="D556" t="s">
         <v>355</v>
       </c>
-      <c r="E556" s="2">
+      <c r="E556" s="3">
         <v>410</v>
       </c>
     </row>
@@ -11036,7 +11037,7 @@
       <c r="D557" t="s">
         <v>356</v>
       </c>
-      <c r="E557" s="2">
+      <c r="E557" s="3">
         <v>-7.79</v>
       </c>
     </row>
@@ -11053,7 +11054,7 @@
       <c r="D558" t="s">
         <v>357</v>
       </c>
-      <c r="E558" s="2">
+      <c r="E558" s="3">
         <v>-0.39</v>
       </c>
     </row>
@@ -11070,7 +11071,7 @@
       <c r="D559" t="s">
         <v>347</v>
       </c>
-      <c r="E559" s="2">
+      <c r="E559" s="3">
         <v>655</v>
       </c>
     </row>
@@ -11087,7 +11088,7 @@
       <c r="D560" t="s">
         <v>348</v>
       </c>
-      <c r="E560" s="2">
+      <c r="E560" s="3">
         <v>3690</v>
       </c>
     </row>
@@ -11104,7 +11105,7 @@
       <c r="D561" t="s">
         <v>349</v>
       </c>
-      <c r="E561" s="2">
+      <c r="E561" s="3">
         <v>18970</v>
       </c>
     </row>
@@ -11121,7 +11122,7 @@
       <c r="D562" t="s">
         <v>350</v>
       </c>
-      <c r="E562" s="2">
+      <c r="E562" s="3">
         <v>12155</v>
       </c>
     </row>
@@ -11138,7 +11139,7 @@
       <c r="D563" t="s">
         <v>343</v>
       </c>
-      <c r="E563" s="2">
+      <c r="E563" s="3">
         <v>-81987.820000000007</v>
       </c>
     </row>
@@ -11155,7 +11156,7 @@
       <c r="D564" t="s">
         <v>344</v>
       </c>
-      <c r="E564" s="2">
+      <c r="E564" s="3">
         <v>1395</v>
       </c>
     </row>
@@ -11172,7 +11173,7 @@
       <c r="D565" t="s">
         <v>345</v>
       </c>
-      <c r="E565" s="2">
+      <c r="E565" s="3">
         <v>-26.51</v>
       </c>
     </row>
@@ -11189,7 +11190,7 @@
       <c r="D566" t="s">
         <v>346</v>
       </c>
-      <c r="E566" s="2">
+      <c r="E566" s="3">
         <v>-1.32</v>
       </c>
     </row>
@@ -11206,7 +11207,7 @@
       <c r="D567" t="s">
         <v>355</v>
       </c>
-      <c r="E567" s="2">
+      <c r="E567" s="3">
         <v>945</v>
       </c>
     </row>
@@ -11223,7 +11224,7 @@
       <c r="D568" t="s">
         <v>356</v>
       </c>
-      <c r="E568" s="2">
+      <c r="E568" s="3">
         <v>-17.96</v>
       </c>
     </row>
@@ -11240,7 +11241,7 @@
       <c r="D569" t="s">
         <v>357</v>
       </c>
-      <c r="E569" s="2">
+      <c r="E569" s="3">
         <v>-0.9</v>
       </c>
     </row>
@@ -11257,7 +11258,7 @@
       <c r="D570" t="s">
         <v>347</v>
       </c>
-      <c r="E570" s="2">
+      <c r="E570" s="3">
         <v>840</v>
       </c>
     </row>
@@ -11274,7 +11275,7 @@
       <c r="D571" t="s">
         <v>348</v>
       </c>
-      <c r="E571" s="2">
+      <c r="E571" s="3">
         <v>2130</v>
       </c>
     </row>
@@ -11291,7 +11292,7 @@
       <c r="D572" t="s">
         <v>349</v>
       </c>
-      <c r="E572" s="2">
+      <c r="E572" s="3">
         <v>19280</v>
       </c>
     </row>
@@ -11308,7 +11309,7 @@
       <c r="D573" t="s">
         <v>350</v>
       </c>
-      <c r="E573" s="2">
+      <c r="E573" s="3">
         <v>15405</v>
       </c>
     </row>
@@ -11325,7 +11326,7 @@
       <c r="D574" t="s">
         <v>351</v>
       </c>
-      <c r="E574" s="2">
+      <c r="E574" s="3">
         <v>710</v>
       </c>
     </row>
@@ -11342,7 +11343,7 @@
       <c r="D575" t="s">
         <v>344</v>
       </c>
-      <c r="E575" s="2">
+      <c r="E575" s="3">
         <v>360</v>
       </c>
     </row>
@@ -11359,7 +11360,7 @@
       <c r="D576" t="s">
         <v>345</v>
       </c>
-      <c r="E576" s="2">
+      <c r="E576" s="3">
         <v>-6.84</v>
       </c>
     </row>
@@ -11376,7 +11377,7 @@
       <c r="D577" t="s">
         <v>346</v>
       </c>
-      <c r="E577" s="2">
+      <c r="E577" s="3">
         <v>-0.34</v>
       </c>
     </row>
@@ -11393,7 +11394,7 @@
       <c r="D578" t="s">
         <v>348</v>
       </c>
-      <c r="E578" s="2">
+      <c r="E578" s="3">
         <v>5285</v>
       </c>
     </row>
@@ -11410,7 +11411,7 @@
       <c r="D579" t="s">
         <v>349</v>
       </c>
-      <c r="E579" s="2">
+      <c r="E579" s="3">
         <v>26725</v>
       </c>
     </row>
@@ -11427,7 +11428,7 @@
       <c r="D580" t="s">
         <v>350</v>
       </c>
-      <c r="E580" s="2">
+      <c r="E580" s="3">
         <v>9815</v>
       </c>
     </row>
@@ -11444,7 +11445,7 @@
       <c r="D581" t="s">
         <v>351</v>
       </c>
-      <c r="E581" s="2">
+      <c r="E581" s="3">
         <v>5305</v>
       </c>
     </row>
@@ -11461,7 +11462,7 @@
       <c r="D582" t="s">
         <v>347</v>
       </c>
-      <c r="E582" s="2">
+      <c r="E582" s="3">
         <v>290</v>
       </c>
     </row>
@@ -11478,7 +11479,7 @@
       <c r="D583" t="s">
         <v>348</v>
       </c>
-      <c r="E583" s="2">
+      <c r="E583" s="3">
         <v>1165</v>
       </c>
     </row>
@@ -11495,7 +11496,7 @@
       <c r="D584" t="s">
         <v>349</v>
       </c>
-      <c r="E584" s="2">
+      <c r="E584" s="3">
         <v>18690</v>
       </c>
     </row>
@@ -11512,7 +11513,7 @@
       <c r="D585" t="s">
         <v>350</v>
       </c>
-      <c r="E585" s="2">
+      <c r="E585" s="3">
         <v>19993</v>
       </c>
     </row>
@@ -11529,7 +11530,7 @@
       <c r="D586" t="s">
         <v>351</v>
       </c>
-      <c r="E586" s="2">
+      <c r="E586" s="3">
         <v>2410</v>
       </c>
     </row>
@@ -11546,7 +11547,7 @@
       <c r="D587" t="s">
         <v>370</v>
       </c>
-      <c r="E587" s="2">
+      <c r="E587" s="3">
         <v>34306.6</v>
       </c>
     </row>
@@ -11563,7 +11564,7 @@
       <c r="D588" t="s">
         <v>371</v>
       </c>
-      <c r="E588" s="2">
+      <c r="E588" s="3">
         <v>61355.01</v>
       </c>
     </row>
@@ -11580,7 +11581,7 @@
       <c r="D589" t="s">
         <v>372</v>
       </c>
-      <c r="E589" s="2">
+      <c r="E589" s="3">
         <v>64852.78</v>
       </c>
     </row>
@@ -11597,7 +11598,7 @@
       <c r="D590" t="s">
         <v>348</v>
       </c>
-      <c r="E590" s="2">
+      <c r="E590" s="3">
         <v>1865</v>
       </c>
     </row>
@@ -11614,7 +11615,7 @@
       <c r="D591" t="s">
         <v>349</v>
       </c>
-      <c r="E591" s="2">
+      <c r="E591" s="3">
         <v>25090</v>
       </c>
     </row>
@@ -11631,7 +11632,7 @@
       <c r="D592" t="s">
         <v>350</v>
       </c>
-      <c r="E592" s="2">
+      <c r="E592" s="3">
         <v>10635</v>
       </c>
     </row>
@@ -11648,7 +11649,7 @@
       <c r="D593" t="s">
         <v>351</v>
       </c>
-      <c r="E593" s="2">
+      <c r="E593" s="3">
         <v>1345</v>
       </c>
     </row>
@@ -11665,7 +11666,7 @@
       <c r="D594" t="s">
         <v>344</v>
       </c>
-      <c r="E594" s="2">
+      <c r="E594" s="3">
         <v>1095</v>
       </c>
     </row>
@@ -11682,7 +11683,7 @@
       <c r="D595" t="s">
         <v>345</v>
       </c>
-      <c r="E595" s="2">
+      <c r="E595" s="3">
         <v>-20.81</v>
       </c>
     </row>
@@ -11699,7 +11700,7 @@
       <c r="D596" t="s">
         <v>346</v>
       </c>
-      <c r="E596" s="2">
+      <c r="E596" s="3">
         <v>-1.04</v>
       </c>
     </row>
@@ -11716,7 +11717,7 @@
       <c r="D597" t="s">
         <v>355</v>
       </c>
-      <c r="E597" s="2">
+      <c r="E597" s="3">
         <v>620</v>
       </c>
     </row>
@@ -11733,7 +11734,7 @@
       <c r="D598" t="s">
         <v>356</v>
       </c>
-      <c r="E598" s="2">
+      <c r="E598" s="3">
         <v>-11.78</v>
       </c>
     </row>
@@ -11750,7 +11751,7 @@
       <c r="D599" t="s">
         <v>357</v>
       </c>
-      <c r="E599" s="2">
+      <c r="E599" s="3">
         <v>-0.59</v>
       </c>
     </row>
@@ -11767,7 +11768,7 @@
       <c r="D600" t="s">
         <v>373</v>
       </c>
-      <c r="E600" s="2">
+      <c r="E600" s="3">
         <v>25966.35</v>
       </c>
     </row>
@@ -11784,7 +11785,7 @@
       <c r="D601" t="s">
         <v>374</v>
       </c>
-      <c r="E601" s="2">
+      <c r="E601" s="3">
         <v>-4</v>
       </c>
     </row>
@@ -11801,7 +11802,7 @@
       <c r="D602" t="s">
         <v>375</v>
       </c>
-      <c r="E602" s="2">
+      <c r="E602" s="3">
         <v>-0.2</v>
       </c>
     </row>
@@ -11818,7 +11819,7 @@
       <c r="D603" t="s">
         <v>376</v>
       </c>
-      <c r="E603" s="2">
+      <c r="E603" s="3">
         <v>-0.02</v>
       </c>
     </row>
@@ -11835,7 +11836,7 @@
       <c r="D604" t="s">
         <v>347</v>
       </c>
-      <c r="E604" s="2">
+      <c r="E604" s="3">
         <v>1645</v>
       </c>
     </row>
@@ -11852,7 +11853,7 @@
       <c r="D605" t="s">
         <v>348</v>
       </c>
-      <c r="E605" s="2">
+      <c r="E605" s="3">
         <v>1735</v>
       </c>
     </row>
@@ -11869,7 +11870,7 @@
       <c r="D606" t="s">
         <v>349</v>
       </c>
-      <c r="E606" s="2">
+      <c r="E606" s="3">
         <v>18015</v>
       </c>
     </row>
@@ -11886,7 +11887,7 @@
       <c r="D607" t="s">
         <v>350</v>
       </c>
-      <c r="E607" s="2">
+      <c r="E607" s="3">
         <v>15147</v>
       </c>
     </row>
@@ -11903,7 +11904,7 @@
       <c r="D608" t="s">
         <v>343</v>
       </c>
-      <c r="E608" s="2">
+      <c r="E608" s="3">
         <v>-394323.43</v>
       </c>
     </row>
@@ -11920,7 +11921,7 @@
       <c r="D609" t="s">
         <v>377</v>
       </c>
-      <c r="E609" s="2">
+      <c r="E609" s="3">
         <v>48442.17</v>
       </c>
     </row>
@@ -11937,7 +11938,7 @@
       <c r="D610" t="s">
         <v>347</v>
       </c>
-      <c r="E610" s="2">
+      <c r="E610" s="3">
         <v>2135</v>
       </c>
     </row>
@@ -11954,7 +11955,7 @@
       <c r="D611" t="s">
         <v>348</v>
       </c>
-      <c r="E611" s="2">
+      <c r="E611" s="3">
         <v>2255</v>
       </c>
     </row>
@@ -11971,7 +11972,7 @@
       <c r="D612" t="s">
         <v>349</v>
       </c>
-      <c r="E612" s="2">
+      <c r="E612" s="3">
         <v>17005</v>
       </c>
     </row>
@@ -11988,7 +11989,7 @@
       <c r="D613" t="s">
         <v>350</v>
       </c>
-      <c r="E613" s="2">
+      <c r="E613" s="3">
         <v>13095</v>
       </c>
     </row>
@@ -12005,7 +12006,7 @@
       <c r="D614" t="s">
         <v>351</v>
       </c>
-      <c r="E614" s="2">
+      <c r="E614" s="3">
         <v>1615</v>
       </c>
     </row>
@@ -12022,7 +12023,7 @@
       <c r="D615" t="s">
         <v>347</v>
       </c>
-      <c r="E615" s="2">
+      <c r="E615" s="3">
         <v>290</v>
       </c>
     </row>
@@ -12039,7 +12040,7 @@
       <c r="D616" t="s">
         <v>348</v>
       </c>
-      <c r="E616" s="2">
+      <c r="E616" s="3">
         <v>2155</v>
       </c>
     </row>
@@ -12056,7 +12057,7 @@
       <c r="D617" t="s">
         <v>349</v>
       </c>
-      <c r="E617" s="2">
+      <c r="E617" s="3">
         <v>23600</v>
       </c>
     </row>
@@ -12073,7 +12074,7 @@
       <c r="D618" t="s">
         <v>350</v>
       </c>
-      <c r="E618" s="2">
+      <c r="E618" s="3">
         <v>13410</v>
       </c>
     </row>
@@ -12090,7 +12091,7 @@
       <c r="D619" t="s">
         <v>351</v>
       </c>
-      <c r="E619" s="2">
+      <c r="E619" s="3">
         <v>395</v>
       </c>
     </row>
@@ -12107,7 +12108,7 @@
       <c r="D620" t="s">
         <v>347</v>
       </c>
-      <c r="E620" s="2">
+      <c r="E620" s="3">
         <v>1145</v>
       </c>
     </row>
@@ -12124,7 +12125,7 @@
       <c r="D621" t="s">
         <v>348</v>
       </c>
-      <c r="E621" s="2">
+      <c r="E621" s="3">
         <v>2345</v>
       </c>
     </row>
@@ -12141,7 +12142,7 @@
       <c r="D622" t="s">
         <v>349</v>
       </c>
-      <c r="E622" s="2">
+      <c r="E622" s="3">
         <v>18060</v>
       </c>
     </row>
@@ -12158,7 +12159,7 @@
       <c r="D623" t="s">
         <v>350</v>
       </c>
-      <c r="E623" s="2">
+      <c r="E623" s="3">
         <v>18445</v>
       </c>
     </row>
@@ -12175,7 +12176,7 @@
       <c r="D624" t="s">
         <v>351</v>
       </c>
-      <c r="E624" s="2">
+      <c r="E624" s="3">
         <v>1570</v>
       </c>
     </row>
@@ -12192,7 +12193,7 @@
       <c r="D625" t="s">
         <v>348</v>
       </c>
-      <c r="E625" s="2">
+      <c r="E625" s="3">
         <v>1215</v>
       </c>
     </row>
@@ -12209,7 +12210,7 @@
       <c r="D626" t="s">
         <v>349</v>
       </c>
-      <c r="E626" s="2">
+      <c r="E626" s="3">
         <v>18820</v>
       </c>
     </row>
@@ -12226,7 +12227,7 @@
       <c r="D627" t="s">
         <v>350</v>
       </c>
-      <c r="E627" s="2">
+      <c r="E627" s="3">
         <v>7490</v>
       </c>
     </row>
@@ -12243,7 +12244,7 @@
       <c r="D628" t="s">
         <v>351</v>
       </c>
-      <c r="E628" s="2">
+      <c r="E628" s="3">
         <v>2185</v>
       </c>
     </row>
@@ -12260,7 +12261,7 @@
       <c r="D629" t="s">
         <v>343</v>
       </c>
-      <c r="E629" s="2">
+      <c r="E629" s="3">
         <v>-195672.17</v>
       </c>
     </row>
@@ -12277,7 +12278,7 @@
       <c r="D630" t="s">
         <v>347</v>
       </c>
-      <c r="E630" s="2">
+      <c r="E630" s="3">
         <v>800</v>
       </c>
     </row>
@@ -12294,7 +12295,7 @@
       <c r="D631" t="s">
         <v>348</v>
       </c>
-      <c r="E631" s="2">
+      <c r="E631" s="3">
         <v>2630</v>
       </c>
     </row>
@@ -12311,7 +12312,7 @@
       <c r="D632" t="s">
         <v>349</v>
       </c>
-      <c r="E632" s="2">
+      <c r="E632" s="3">
         <v>23900</v>
       </c>
     </row>
@@ -12328,7 +12329,7 @@
       <c r="D633" t="s">
         <v>350</v>
       </c>
-      <c r="E633" s="2">
+      <c r="E633" s="3">
         <v>9180</v>
       </c>
     </row>
@@ -12345,7 +12346,7 @@
       <c r="D634" t="s">
         <v>351</v>
       </c>
-      <c r="E634" s="2">
+      <c r="E634" s="3">
         <v>1525</v>
       </c>
     </row>
@@ -12362,7 +12363,7 @@
       <c r="D635" t="s">
         <v>348</v>
       </c>
-      <c r="E635" s="2">
+      <c r="E635" s="3">
         <v>2980</v>
       </c>
     </row>
@@ -12379,7 +12380,7 @@
       <c r="D636" t="s">
         <v>349</v>
       </c>
-      <c r="E636" s="2">
+      <c r="E636" s="3">
         <v>15140</v>
       </c>
     </row>
@@ -12396,7 +12397,7 @@
       <c r="D637" t="s">
         <v>350</v>
       </c>
-      <c r="E637" s="2">
+      <c r="E637" s="3">
         <v>14450</v>
       </c>
     </row>
@@ -12413,7 +12414,7 @@
       <c r="D638" t="s">
         <v>351</v>
       </c>
-      <c r="E638" s="2">
+      <c r="E638" s="3">
         <v>720</v>
       </c>
     </row>
@@ -12430,7 +12431,7 @@
       <c r="D639" t="s">
         <v>343</v>
       </c>
-      <c r="E639" s="2">
+      <c r="E639" s="3">
         <v>-71325</v>
       </c>
     </row>
@@ -12447,7 +12448,7 @@
       <c r="D640" t="s">
         <v>347</v>
       </c>
-      <c r="E640" s="2">
+      <c r="E640" s="3">
         <v>360</v>
       </c>
     </row>
@@ -12464,7 +12465,7 @@
       <c r="D641" t="s">
         <v>348</v>
       </c>
-      <c r="E641" s="2">
+      <c r="E641" s="3">
         <v>2260</v>
       </c>
     </row>
@@ -12481,7 +12482,7 @@
       <c r="D642" t="s">
         <v>349</v>
       </c>
-      <c r="E642" s="2">
+      <c r="E642" s="3">
         <v>11400</v>
       </c>
     </row>
@@ -12498,7 +12499,7 @@
       <c r="D643" t="s">
         <v>350</v>
       </c>
-      <c r="E643" s="2">
+      <c r="E643" s="3">
         <v>18975</v>
       </c>
     </row>
@@ -12515,7 +12516,7 @@
       <c r="D644" t="s">
         <v>351</v>
       </c>
-      <c r="E644" s="2">
+      <c r="E644" s="3">
         <v>310</v>
       </c>
     </row>
@@ -12532,7 +12533,7 @@
       <c r="D645" t="s">
         <v>344</v>
       </c>
-      <c r="E645" s="2">
+      <c r="E645" s="3">
         <v>310</v>
       </c>
     </row>
@@ -12549,7 +12550,7 @@
       <c r="D646" t="s">
         <v>345</v>
       </c>
-      <c r="E646" s="2">
+      <c r="E646" s="3">
         <v>-5.89</v>
       </c>
     </row>
@@ -12566,7 +12567,7 @@
       <c r="D647" t="s">
         <v>346</v>
       </c>
-      <c r="E647" s="2">
+      <c r="E647" s="3">
         <v>-0.28999999999999998</v>
       </c>
     </row>
@@ -12583,7 +12584,7 @@
       <c r="D648" t="s">
         <v>343</v>
       </c>
-      <c r="E648" s="2">
+      <c r="E648" s="3">
         <v>-33608.82</v>
       </c>
     </row>
@@ -12600,7 +12601,7 @@
       <c r="D649" t="s">
         <v>379</v>
       </c>
-      <c r="E649" s="2">
+      <c r="E649" s="3">
         <v>39523.42</v>
       </c>
     </row>
@@ -12617,7 +12618,7 @@
       <c r="D650" t="s">
         <v>348</v>
       </c>
-      <c r="E650" s="2">
+      <c r="E650" s="3">
         <v>1391</v>
       </c>
     </row>
@@ -12634,7 +12635,7 @@
       <c r="D651" t="s">
         <v>349</v>
       </c>
-      <c r="E651" s="2">
+      <c r="E651" s="3">
         <v>18614.5</v>
       </c>
     </row>
@@ -12651,7 +12652,7 @@
       <c r="D652" t="s">
         <v>350</v>
       </c>
-      <c r="E652" s="2">
+      <c r="E652" s="3">
         <v>15160</v>
       </c>
     </row>
@@ -12668,7 +12669,7 @@
       <c r="D653" t="s">
         <v>351</v>
       </c>
-      <c r="E653" s="2">
+      <c r="E653" s="3">
         <v>1125</v>
       </c>
     </row>
@@ -12685,7 +12686,7 @@
       <c r="D654" t="s">
         <v>344</v>
       </c>
-      <c r="E654" s="2">
+      <c r="E654" s="3">
         <v>1800</v>
       </c>
     </row>
@@ -12702,7 +12703,7 @@
       <c r="D655" t="s">
         <v>345</v>
       </c>
-      <c r="E655" s="2">
+      <c r="E655" s="3">
         <v>-34.200000000000003</v>
       </c>
     </row>
@@ -12719,7 +12720,7 @@
       <c r="D656" t="s">
         <v>346</v>
       </c>
-      <c r="E656" s="2">
+      <c r="E656" s="3">
         <v>-1.71</v>
       </c>
     </row>
@@ -12736,7 +12737,7 @@
       <c r="D657" t="s">
         <v>344</v>
       </c>
-      <c r="E657" s="2">
+      <c r="E657" s="3">
         <v>1200</v>
       </c>
     </row>
@@ -12753,7 +12754,7 @@
       <c r="D658" t="s">
         <v>345</v>
       </c>
-      <c r="E658" s="2">
+      <c r="E658" s="3">
         <v>-22.8</v>
       </c>
     </row>
@@ -12770,7 +12771,7 @@
       <c r="D659" t="s">
         <v>346</v>
       </c>
-      <c r="E659" s="2">
+      <c r="E659" s="3">
         <v>-1.1399999999999999</v>
       </c>
     </row>
@@ -12787,7 +12788,7 @@
       <c r="D660" t="s">
         <v>355</v>
       </c>
-      <c r="E660" s="2">
+      <c r="E660" s="3">
         <v>360</v>
       </c>
     </row>
@@ -12804,7 +12805,7 @@
       <c r="D661" t="s">
         <v>356</v>
       </c>
-      <c r="E661" s="2">
+      <c r="E661" s="3">
         <v>-6.84</v>
       </c>
     </row>
@@ -12821,7 +12822,7 @@
       <c r="D662" t="s">
         <v>357</v>
       </c>
-      <c r="E662" s="2">
+      <c r="E662" s="3">
         <v>-0.34</v>
       </c>
     </row>
@@ -12838,7 +12839,7 @@
       <c r="D663" t="s">
         <v>347</v>
       </c>
-      <c r="E663" s="2">
+      <c r="E663" s="3">
         <v>675</v>
       </c>
     </row>
@@ -12855,7 +12856,7 @@
       <c r="D664" t="s">
         <v>348</v>
       </c>
-      <c r="E664" s="2">
+      <c r="E664" s="3">
         <v>1150</v>
       </c>
     </row>
@@ -12872,7 +12873,7 @@
       <c r="D665" t="s">
         <v>349</v>
       </c>
-      <c r="E665" s="2">
+      <c r="E665" s="3">
         <v>10045</v>
       </c>
     </row>
@@ -12889,7 +12890,7 @@
       <c r="D666" t="s">
         <v>350</v>
       </c>
-      <c r="E666" s="2">
+      <c r="E666" s="3">
         <v>13130</v>
       </c>
     </row>
@@ -12906,7 +12907,7 @@
       <c r="D667" t="s">
         <v>351</v>
       </c>
-      <c r="E667" s="2">
+      <c r="E667" s="3">
         <v>1815</v>
       </c>
     </row>
@@ -12923,7 +12924,7 @@
       <c r="D668" t="s">
         <v>344</v>
       </c>
-      <c r="E668" s="2">
+      <c r="E668" s="3">
         <v>650</v>
       </c>
     </row>
@@ -12940,7 +12941,7 @@
       <c r="D669" t="s">
         <v>345</v>
       </c>
-      <c r="E669" s="2">
+      <c r="E669" s="3">
         <v>-12.35</v>
       </c>
     </row>
@@ -12957,7 +12958,7 @@
       <c r="D670" t="s">
         <v>346</v>
       </c>
-      <c r="E670" s="2">
+      <c r="E670" s="3">
         <v>-0.62</v>
       </c>
     </row>
@@ -12974,7 +12975,7 @@
       <c r="D671" t="s">
         <v>355</v>
       </c>
-      <c r="E671" s="2">
+      <c r="E671" s="3">
         <v>1362.5</v>
       </c>
     </row>
@@ -12991,7 +12992,7 @@
       <c r="D672" t="s">
         <v>356</v>
       </c>
-      <c r="E672" s="2">
+      <c r="E672" s="3">
         <v>-25.89</v>
       </c>
     </row>
@@ -13008,7 +13009,7 @@
       <c r="D673" t="s">
         <v>357</v>
       </c>
-      <c r="E673" s="2">
+      <c r="E673" s="3">
         <v>-1.29</v>
       </c>
     </row>
@@ -13025,7 +13026,7 @@
       <c r="D674" t="s">
         <v>344</v>
       </c>
-      <c r="E674" s="2">
+      <c r="E674" s="3">
         <v>290</v>
       </c>
     </row>
@@ -13042,7 +13043,7 @@
       <c r="D675" t="s">
         <v>345</v>
       </c>
-      <c r="E675" s="2">
+      <c r="E675" s="3">
         <v>-5.51</v>
       </c>
     </row>
@@ -13059,7 +13060,7 @@
       <c r="D676" t="s">
         <v>346</v>
       </c>
-      <c r="E676" s="2">
+      <c r="E676" s="3">
         <v>-0.28000000000000003</v>
       </c>
     </row>
@@ -13076,7 +13077,7 @@
       <c r="D677" t="s">
         <v>350</v>
       </c>
-      <c r="E677" s="2">
+      <c r="E677" s="3">
         <v>7270</v>
       </c>
     </row>
@@ -13093,7 +13094,7 @@
       <c r="D678" t="s">
         <v>348</v>
       </c>
-      <c r="E678" s="2">
+      <c r="E678" s="3">
         <v>775</v>
       </c>
     </row>
@@ -13110,7 +13111,7 @@
       <c r="D679" t="s">
         <v>349</v>
       </c>
-      <c r="E679" s="2">
+      <c r="E679" s="3">
         <v>21575</v>
       </c>
     </row>
@@ -13127,7 +13128,7 @@
       <c r="D680" t="s">
         <v>364</v>
       </c>
-      <c r="E680" s="2">
+      <c r="E680" s="3">
         <v>465</v>
       </c>
     </row>
@@ -13144,7 +13145,7 @@
       <c r="D681" t="s">
         <v>343</v>
       </c>
-      <c r="E681" s="2">
+      <c r="E681" s="3">
         <v>-138263.45000000001</v>
       </c>
     </row>
@@ -13161,7 +13162,7 @@
       <c r="D682" t="s">
         <v>347</v>
       </c>
-      <c r="E682" s="2">
+      <c r="E682" s="3">
         <v>430</v>
       </c>
     </row>
@@ -13178,7 +13179,7 @@
       <c r="D683" t="s">
         <v>348</v>
       </c>
-      <c r="E683" s="2">
+      <c r="E683" s="3">
         <v>950</v>
       </c>
     </row>
@@ -13195,7 +13196,7 @@
       <c r="D684" t="s">
         <v>349</v>
       </c>
-      <c r="E684" s="2">
+      <c r="E684" s="3">
         <v>22405</v>
       </c>
     </row>
@@ -13212,7 +13213,7 @@
       <c r="D685" t="s">
         <v>350</v>
       </c>
-      <c r="E685" s="2">
+      <c r="E685" s="3">
         <v>13552.5</v>
       </c>
     </row>
@@ -13229,7 +13230,7 @@
       <c r="D686" t="s">
         <v>351</v>
       </c>
-      <c r="E686" s="2">
+      <c r="E686" s="3">
         <v>1407.5</v>
       </c>
     </row>
@@ -13246,7 +13247,7 @@
       <c r="D687" t="s">
         <v>355</v>
       </c>
-      <c r="E687" s="2">
+      <c r="E687" s="3">
         <v>800</v>
       </c>
     </row>
@@ -13263,7 +13264,7 @@
       <c r="D688" t="s">
         <v>356</v>
       </c>
-      <c r="E688" s="2">
+      <c r="E688" s="3">
         <v>-15.2</v>
       </c>
     </row>
@@ -13280,7 +13281,7 @@
       <c r="D689" t="s">
         <v>357</v>
       </c>
-      <c r="E689" s="2">
+      <c r="E689" s="3">
         <v>-0.76</v>
       </c>
     </row>
@@ -13297,7 +13298,7 @@
       <c r="D690" t="s">
         <v>343</v>
       </c>
-      <c r="E690" s="2">
+      <c r="E690" s="3">
         <v>-39529.040000000001</v>
       </c>
     </row>
@@ -13314,7 +13315,7 @@
       <c r="D691" t="s">
         <v>347</v>
       </c>
-      <c r="E691" s="2">
+      <c r="E691" s="3">
         <v>825</v>
       </c>
     </row>
@@ -13331,7 +13332,7 @@
       <c r="D692" t="s">
         <v>348</v>
       </c>
-      <c r="E692" s="2">
+      <c r="E692" s="3">
         <v>4623</v>
       </c>
     </row>
@@ -13348,7 +13349,7 @@
       <c r="D693" t="s">
         <v>349</v>
       </c>
-      <c r="E693" s="2">
+      <c r="E693" s="3">
         <v>19004</v>
       </c>
     </row>
@@ -13365,7 +13366,7 @@
       <c r="D694" t="s">
         <v>350</v>
       </c>
-      <c r="E694" s="2">
+      <c r="E694" s="3">
         <v>16638</v>
       </c>
     </row>
@@ -13382,7 +13383,7 @@
       <c r="D695" t="s">
         <v>351</v>
       </c>
-      <c r="E695" s="2">
+      <c r="E695" s="3">
         <v>1080</v>
       </c>
     </row>
@@ -13399,1023 +13400,9 @@
       <c r="D696" t="s">
         <v>343</v>
       </c>
-      <c r="E696" s="2">
+      <c r="E696" s="3">
         <v>-42170</v>
       </c>
-    </row>
-    <row r="697" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="E697" s="2"/>
-    </row>
-    <row r="698" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="E698" s="2"/>
-    </row>
-    <row r="699" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="E699" s="2"/>
-    </row>
-    <row r="700" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="E700" s="2"/>
-    </row>
-    <row r="701" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="E701" s="2"/>
-    </row>
-    <row r="702" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="E702" s="2"/>
-    </row>
-    <row r="703" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="E703" s="2"/>
-    </row>
-    <row r="704" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="E704" s="2"/>
-    </row>
-    <row r="705" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E705" s="2"/>
-    </row>
-    <row r="706" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E706" s="2"/>
-    </row>
-    <row r="707" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E707" s="2"/>
-    </row>
-    <row r="708" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E708" s="2"/>
-    </row>
-    <row r="709" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E709" s="2"/>
-    </row>
-    <row r="710" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E710" s="2"/>
-    </row>
-    <row r="711" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E711" s="2"/>
-    </row>
-    <row r="712" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E712" s="2"/>
-    </row>
-    <row r="713" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E713" s="2"/>
-    </row>
-    <row r="714" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E714" s="2"/>
-    </row>
-    <row r="715" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E715" s="2"/>
-    </row>
-    <row r="716" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E716" s="2"/>
-    </row>
-    <row r="717" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E717" s="2"/>
-    </row>
-    <row r="718" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E718" s="2"/>
-    </row>
-    <row r="719" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E719" s="2"/>
-    </row>
-    <row r="720" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E720" s="2"/>
-    </row>
-    <row r="721" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E721" s="2"/>
-    </row>
-    <row r="722" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E722" s="2"/>
-    </row>
-    <row r="723" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E723" s="2"/>
-    </row>
-    <row r="724" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E724" s="2"/>
-    </row>
-    <row r="725" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E725" s="2"/>
-    </row>
-    <row r="726" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E726" s="2"/>
-    </row>
-    <row r="727" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E727" s="2"/>
-    </row>
-    <row r="728" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E728" s="2"/>
-    </row>
-    <row r="729" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E729" s="2"/>
-    </row>
-    <row r="730" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E730" s="2"/>
-    </row>
-    <row r="731" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E731" s="2"/>
-    </row>
-    <row r="732" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E732" s="2"/>
-    </row>
-    <row r="733" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E733" s="2"/>
-    </row>
-    <row r="734" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E734" s="2"/>
-    </row>
-    <row r="735" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E735" s="2"/>
-    </row>
-    <row r="736" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E736" s="2"/>
-    </row>
-    <row r="737" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E737" s="2"/>
-    </row>
-    <row r="738" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E738" s="2"/>
-    </row>
-    <row r="739" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E739" s="2"/>
-    </row>
-    <row r="740" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E740" s="2"/>
-    </row>
-    <row r="741" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E741" s="2"/>
-    </row>
-    <row r="742" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E742" s="2"/>
-    </row>
-    <row r="743" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E743" s="2"/>
-    </row>
-    <row r="744" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E744" s="2"/>
-    </row>
-    <row r="745" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E745" s="2"/>
-    </row>
-    <row r="746" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E746" s="2"/>
-    </row>
-    <row r="747" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E747" s="2"/>
-    </row>
-    <row r="748" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E748" s="2"/>
-    </row>
-    <row r="749" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E749" s="2"/>
-    </row>
-    <row r="750" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E750" s="2"/>
-    </row>
-    <row r="751" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E751" s="2"/>
-    </row>
-    <row r="752" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E752" s="2"/>
-    </row>
-    <row r="753" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E753" s="2"/>
-    </row>
-    <row r="754" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E754" s="2"/>
-    </row>
-    <row r="755" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E755" s="2"/>
-    </row>
-    <row r="756" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E756" s="2"/>
-    </row>
-    <row r="757" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E757" s="2"/>
-    </row>
-    <row r="758" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E758" s="2"/>
-    </row>
-    <row r="759" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E759" s="2"/>
-    </row>
-    <row r="760" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E760" s="2"/>
-    </row>
-    <row r="761" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E761" s="2"/>
-    </row>
-    <row r="762" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E762" s="2"/>
-    </row>
-    <row r="763" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E763" s="2"/>
-    </row>
-    <row r="764" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E764" s="2"/>
-    </row>
-    <row r="765" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E765" s="2"/>
-    </row>
-    <row r="766" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E766" s="2"/>
-    </row>
-    <row r="767" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E767" s="2"/>
-    </row>
-    <row r="768" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E768" s="2"/>
-    </row>
-    <row r="769" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E769" s="2"/>
-    </row>
-    <row r="770" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E770" s="2"/>
-    </row>
-    <row r="771" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E771" s="2"/>
-    </row>
-    <row r="772" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E772" s="2"/>
-    </row>
-    <row r="773" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E773" s="2"/>
-    </row>
-    <row r="774" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E774" s="2"/>
-    </row>
-    <row r="775" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E775" s="2"/>
-    </row>
-    <row r="776" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E776" s="2"/>
-    </row>
-    <row r="777" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E777" s="2"/>
-    </row>
-    <row r="778" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E778" s="2"/>
-    </row>
-    <row r="779" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E779" s="2"/>
-    </row>
-    <row r="780" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E780" s="2"/>
-    </row>
-    <row r="781" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E781" s="2"/>
-    </row>
-    <row r="782" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E782" s="2"/>
-    </row>
-    <row r="783" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E783" s="2"/>
-    </row>
-    <row r="784" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E784" s="2"/>
-    </row>
-    <row r="785" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E785" s="2"/>
-    </row>
-    <row r="786" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E786" s="2"/>
-    </row>
-    <row r="787" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E787" s="2"/>
-    </row>
-    <row r="788" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E788" s="2"/>
-    </row>
-    <row r="789" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E789" s="2"/>
-    </row>
-    <row r="790" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E790" s="2"/>
-    </row>
-    <row r="791" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E791" s="2"/>
-    </row>
-    <row r="792" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E792" s="2"/>
-    </row>
-    <row r="793" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E793" s="2"/>
-    </row>
-    <row r="794" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E794" s="2"/>
-    </row>
-    <row r="795" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E795" s="2"/>
-    </row>
-    <row r="796" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E796" s="2"/>
-    </row>
-    <row r="797" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E797" s="2"/>
-    </row>
-    <row r="798" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E798" s="2"/>
-    </row>
-    <row r="799" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E799" s="2"/>
-    </row>
-    <row r="800" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E800" s="2"/>
-    </row>
-    <row r="801" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E801" s="2"/>
-    </row>
-    <row r="802" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E802" s="2"/>
-    </row>
-    <row r="803" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E803" s="2"/>
-    </row>
-    <row r="804" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E804" s="2"/>
-    </row>
-    <row r="805" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E805" s="2"/>
-    </row>
-    <row r="806" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E806" s="2"/>
-    </row>
-    <row r="807" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E807" s="2"/>
-    </row>
-    <row r="808" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E808" s="2"/>
-    </row>
-    <row r="809" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E809" s="2"/>
-    </row>
-    <row r="810" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E810" s="2"/>
-    </row>
-    <row r="811" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E811" s="2"/>
-    </row>
-    <row r="812" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E812" s="2"/>
-    </row>
-    <row r="813" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E813" s="2"/>
-    </row>
-    <row r="814" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E814" s="2"/>
-    </row>
-    <row r="815" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E815" s="2"/>
-    </row>
-    <row r="816" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E816" s="2"/>
-    </row>
-    <row r="817" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E817" s="2"/>
-    </row>
-    <row r="818" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E818" s="2"/>
-    </row>
-    <row r="819" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E819" s="2"/>
-    </row>
-    <row r="820" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E820" s="2"/>
-    </row>
-    <row r="821" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E821" s="2"/>
-    </row>
-    <row r="822" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E822" s="2"/>
-    </row>
-    <row r="823" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E823" s="2"/>
-    </row>
-    <row r="824" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E824" s="2"/>
-    </row>
-    <row r="825" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E825" s="2"/>
-    </row>
-    <row r="826" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E826" s="2"/>
-    </row>
-    <row r="827" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E827" s="2"/>
-    </row>
-    <row r="828" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E828" s="2"/>
-    </row>
-    <row r="829" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E829" s="2"/>
-    </row>
-    <row r="830" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E830" s="2"/>
-    </row>
-    <row r="831" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E831" s="2"/>
-    </row>
-    <row r="832" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E832" s="2"/>
-    </row>
-    <row r="833" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E833" s="2"/>
-    </row>
-    <row r="834" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E834" s="2"/>
-    </row>
-    <row r="835" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E835" s="2"/>
-    </row>
-    <row r="836" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E836" s="2"/>
-    </row>
-    <row r="837" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E837" s="2"/>
-    </row>
-    <row r="838" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E838" s="2"/>
-    </row>
-    <row r="839" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E839" s="2"/>
-    </row>
-    <row r="840" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E840" s="2"/>
-    </row>
-    <row r="841" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E841" s="2"/>
-    </row>
-    <row r="842" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E842" s="2"/>
-    </row>
-    <row r="843" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E843" s="2"/>
-    </row>
-    <row r="844" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E844" s="2"/>
-    </row>
-    <row r="845" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E845" s="2"/>
-    </row>
-    <row r="846" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E846" s="2"/>
-    </row>
-    <row r="847" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E847" s="2"/>
-    </row>
-    <row r="848" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E848" s="2"/>
-    </row>
-    <row r="849" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E849" s="2"/>
-    </row>
-    <row r="850" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E850" s="2"/>
-    </row>
-    <row r="851" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E851" s="2"/>
-    </row>
-    <row r="852" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E852" s="2"/>
-    </row>
-    <row r="853" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E853" s="2"/>
-    </row>
-    <row r="854" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E854" s="2"/>
-    </row>
-    <row r="855" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E855" s="2"/>
-    </row>
-    <row r="856" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E856" s="2"/>
-    </row>
-    <row r="857" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E857" s="2"/>
-    </row>
-    <row r="858" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E858" s="2"/>
-    </row>
-    <row r="859" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E859" s="2"/>
-    </row>
-    <row r="860" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E860" s="2"/>
-    </row>
-    <row r="861" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E861" s="2"/>
-    </row>
-    <row r="862" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E862" s="2"/>
-    </row>
-    <row r="863" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E863" s="2"/>
-    </row>
-    <row r="864" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E864" s="2"/>
-    </row>
-    <row r="865" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E865" s="2"/>
-    </row>
-    <row r="866" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E866" s="2"/>
-    </row>
-    <row r="867" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E867" s="2"/>
-    </row>
-    <row r="868" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E868" s="2"/>
-    </row>
-    <row r="869" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E869" s="2"/>
-    </row>
-    <row r="870" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E870" s="2"/>
-    </row>
-    <row r="871" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E871" s="2"/>
-    </row>
-    <row r="872" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E872" s="2"/>
-    </row>
-    <row r="873" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E873" s="2"/>
-    </row>
-    <row r="874" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E874" s="2"/>
-    </row>
-    <row r="875" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E875" s="2"/>
-    </row>
-    <row r="876" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E876" s="2"/>
-    </row>
-    <row r="877" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E877" s="2"/>
-    </row>
-    <row r="878" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E878" s="2"/>
-    </row>
-    <row r="879" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E879" s="2"/>
-    </row>
-    <row r="880" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E880" s="2"/>
-    </row>
-    <row r="881" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E881" s="2"/>
-    </row>
-    <row r="882" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E882" s="2"/>
-    </row>
-    <row r="883" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E883" s="2"/>
-    </row>
-    <row r="884" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E884" s="2"/>
-    </row>
-    <row r="885" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E885" s="2"/>
-    </row>
-    <row r="886" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E886" s="2"/>
-    </row>
-    <row r="887" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E887" s="2"/>
-    </row>
-    <row r="888" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E888" s="2"/>
-    </row>
-    <row r="889" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E889" s="2"/>
-    </row>
-    <row r="890" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E890" s="2"/>
-    </row>
-    <row r="891" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E891" s="2"/>
-    </row>
-    <row r="892" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E892" s="2"/>
-    </row>
-    <row r="893" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E893" s="2"/>
-    </row>
-    <row r="894" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E894" s="2"/>
-    </row>
-    <row r="895" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E895" s="2"/>
-    </row>
-    <row r="896" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E896" s="2"/>
-    </row>
-    <row r="897" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E897" s="2"/>
-    </row>
-    <row r="898" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E898" s="2"/>
-    </row>
-    <row r="899" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E899" s="2"/>
-    </row>
-    <row r="900" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E900" s="2"/>
-    </row>
-    <row r="901" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E901" s="2"/>
-    </row>
-    <row r="902" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E902" s="2"/>
-    </row>
-    <row r="903" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E903" s="2"/>
-    </row>
-    <row r="904" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E904" s="2"/>
-    </row>
-    <row r="905" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E905" s="2"/>
-    </row>
-    <row r="906" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E906" s="2"/>
-    </row>
-    <row r="907" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E907" s="2"/>
-    </row>
-    <row r="908" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E908" s="2"/>
-    </row>
-    <row r="909" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E909" s="2"/>
-    </row>
-    <row r="910" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E910" s="2"/>
-    </row>
-    <row r="911" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E911" s="2"/>
-    </row>
-    <row r="912" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E912" s="2"/>
-    </row>
-    <row r="913" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E913" s="2"/>
-    </row>
-    <row r="914" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E914" s="2"/>
-    </row>
-    <row r="915" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E915" s="2"/>
-    </row>
-    <row r="916" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E916" s="2"/>
-    </row>
-    <row r="917" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E917" s="2"/>
-    </row>
-    <row r="918" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E918" s="2"/>
-    </row>
-    <row r="919" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E919" s="2"/>
-    </row>
-    <row r="920" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E920" s="2"/>
-    </row>
-    <row r="921" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E921" s="2"/>
-    </row>
-    <row r="922" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E922" s="2"/>
-    </row>
-    <row r="923" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E923" s="2"/>
-    </row>
-    <row r="924" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E924" s="2"/>
-    </row>
-    <row r="925" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E925" s="2"/>
-    </row>
-    <row r="926" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E926" s="2"/>
-    </row>
-    <row r="927" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E927" s="2"/>
-    </row>
-    <row r="928" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E928" s="2"/>
-    </row>
-    <row r="929" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E929" s="2"/>
-    </row>
-    <row r="930" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E930" s="2"/>
-    </row>
-    <row r="931" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E931" s="2"/>
-    </row>
-    <row r="932" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E932" s="2"/>
-    </row>
-    <row r="933" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E933" s="2"/>
-    </row>
-    <row r="934" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E934" s="2"/>
-    </row>
-    <row r="935" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E935" s="2"/>
-    </row>
-    <row r="936" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E936" s="2"/>
-    </row>
-    <row r="937" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E937" s="2"/>
-    </row>
-    <row r="938" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E938" s="2"/>
-    </row>
-    <row r="939" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E939" s="2"/>
-    </row>
-    <row r="940" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E940" s="2"/>
-    </row>
-    <row r="941" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E941" s="2"/>
-    </row>
-    <row r="942" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E942" s="2"/>
-    </row>
-    <row r="943" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E943" s="2"/>
-    </row>
-    <row r="944" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E944" s="2"/>
-    </row>
-    <row r="945" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E945" s="2"/>
-    </row>
-    <row r="946" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E946" s="2"/>
-    </row>
-    <row r="947" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E947" s="2"/>
-    </row>
-    <row r="948" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E948" s="2"/>
-    </row>
-    <row r="949" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E949" s="2"/>
-    </row>
-    <row r="950" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E950" s="2"/>
-    </row>
-    <row r="951" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E951" s="2"/>
-    </row>
-    <row r="952" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E952" s="2"/>
-    </row>
-    <row r="953" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E953" s="2"/>
-    </row>
-    <row r="954" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E954" s="2"/>
-    </row>
-    <row r="955" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E955" s="2"/>
-    </row>
-    <row r="956" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E956" s="2"/>
-    </row>
-    <row r="957" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E957" s="2"/>
-    </row>
-    <row r="958" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E958" s="2"/>
-    </row>
-    <row r="959" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E959" s="2"/>
-    </row>
-    <row r="960" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E960" s="2"/>
-    </row>
-    <row r="961" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E961" s="2"/>
-    </row>
-    <row r="962" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E962" s="2"/>
-    </row>
-    <row r="963" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E963" s="2"/>
-    </row>
-    <row r="964" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E964" s="2"/>
-    </row>
-    <row r="965" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E965" s="2"/>
-    </row>
-    <row r="966" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E966" s="2"/>
-    </row>
-    <row r="967" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E967" s="2"/>
-    </row>
-    <row r="968" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E968" s="2"/>
-    </row>
-    <row r="969" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E969" s="2"/>
-    </row>
-    <row r="970" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E970" s="2"/>
-    </row>
-    <row r="971" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E971" s="2"/>
-    </row>
-    <row r="972" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E972" s="2"/>
-    </row>
-    <row r="973" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E973" s="2"/>
-    </row>
-    <row r="974" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E974" s="2"/>
-    </row>
-    <row r="975" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E975" s="2"/>
-    </row>
-    <row r="976" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E976" s="2"/>
-    </row>
-    <row r="977" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E977" s="2"/>
-    </row>
-    <row r="978" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E978" s="2"/>
-    </row>
-    <row r="979" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E979" s="2"/>
-    </row>
-    <row r="980" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E980" s="2"/>
-    </row>
-    <row r="981" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E981" s="2"/>
-    </row>
-    <row r="982" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E982" s="2"/>
-    </row>
-    <row r="983" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E983" s="2"/>
-    </row>
-    <row r="984" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E984" s="2"/>
-    </row>
-    <row r="985" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E985" s="2"/>
-    </row>
-    <row r="986" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E986" s="2"/>
-    </row>
-    <row r="987" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E987" s="2"/>
-    </row>
-    <row r="988" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E988" s="2"/>
-    </row>
-    <row r="989" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E989" s="2"/>
-    </row>
-    <row r="990" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E990" s="2"/>
-    </row>
-    <row r="991" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E991" s="2"/>
-    </row>
-    <row r="992" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E992" s="2"/>
-    </row>
-    <row r="993" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E993" s="2"/>
-    </row>
-    <row r="994" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E994" s="2"/>
-    </row>
-    <row r="995" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E995" s="2"/>
-    </row>
-    <row r="996" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E996" s="2"/>
-    </row>
-    <row r="997" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E997" s="2"/>
-    </row>
-    <row r="998" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E998" s="2"/>
-    </row>
-    <row r="999" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E999" s="2"/>
-    </row>
-    <row r="1000" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E1000" s="2"/>
-    </row>
-    <row r="1001" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E1001" s="2"/>
-    </row>
-    <row r="1002" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E1002" s="2"/>
-    </row>
-    <row r="1003" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E1003" s="2"/>
-    </row>
-    <row r="1004" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E1004" s="2"/>
-    </row>
-    <row r="1005" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E1005" s="2"/>
-    </row>
-    <row r="1006" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E1006" s="2"/>
-    </row>
-    <row r="1007" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E1007" s="2"/>
-    </row>
-    <row r="1008" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E1008" s="2"/>
-    </row>
-    <row r="1009" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E1009" s="2"/>
-    </row>
-    <row r="1010" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E1010" s="2"/>
-    </row>
-    <row r="1011" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E1011" s="2"/>
-    </row>
-    <row r="1012" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E1012" s="2"/>
-    </row>
-    <row r="1013" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E1013" s="2"/>
-    </row>
-    <row r="1014" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E1014" s="2"/>
-    </row>
-    <row r="1015" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E1015" s="2"/>
-    </row>
-    <row r="1016" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E1016" s="2"/>
-    </row>
-    <row r="1017" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E1017" s="2"/>
-    </row>
-    <row r="1018" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E1018" s="2"/>
-    </row>
-    <row r="1019" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E1019" s="2"/>
-    </row>
-    <row r="1020" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E1020" s="2"/>
-    </row>
-    <row r="1021" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E1021" s="2"/>
-    </row>
-    <row r="1022" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E1022" s="2"/>
-    </row>
-    <row r="1023" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E1023" s="2"/>
-    </row>
-    <row r="1024" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E1024" s="2"/>
-    </row>
-    <row r="1025" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E1025" s="2"/>
-    </row>
-    <row r="1026" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E1026" s="2"/>
-    </row>
-    <row r="1027" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E1027" s="2"/>
-    </row>
-    <row r="1028" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E1028" s="2"/>
-    </row>
-    <row r="1029" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E1029" s="2"/>
-    </row>
-    <row r="1030" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E1030" s="2"/>
-    </row>
-    <row r="1031" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E1031" s="2"/>
-    </row>
-    <row r="1032" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E1032" s="2"/>
-    </row>
-    <row r="1033" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E1033" s="2"/>
-    </row>
-    <row r="1034" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E1034" s="2"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:E1034" xr:uid="{DDBFB41B-2FC1-43D5-8050-DA58EFE3045A}"/>

--- a/Odeme.xlsx
+++ b/Odeme.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://clbexch-my.sharepoint.com/personal/serdar_gunizi_celebiaviation_com/Documents/Personel/Programming/Python/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="8_{028C6BA9-E504-4CA6-9D1E-EA28749E249E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{316875F9-CC7C-49DE-B846-FF5FC587BAC4}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="8_{028C6BA9-E504-4CA6-9D1E-EA28749E249E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7A6368E5-7507-4D6B-B204-3065F7D9108A}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{8342C7F8-B62A-427E-B7BD-BDD92660C0AC}"/>
   </bookViews>
